--- a/data/initial_state_2026.xlsx
+++ b/data/initial_state_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="14540" activeTab="3"/>
+    <workbookView windowWidth="30240" windowHeight="14540"/>
   </bookViews>
   <sheets>
     <sheet name="global.pars" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="736">
   <si>
     <t>label</t>
   </si>
@@ -104,10 +104,10 @@
     <t>IO Coefficient Decrease of the B Matrix</t>
   </si>
   <si>
-    <t>reduction</t>
+    <t>rho</t>
   </si>
   <si>
-    <t>Reduction Parameter for Shocks</t>
+    <t>Shock Parameter</t>
   </si>
   <si>
     <t>sigma_en</t>
@@ -1521,9 +1521,6 @@
   </si>
   <si>
     <t>Productivity</t>
-  </si>
-  <si>
-    <t>rho</t>
   </si>
   <si>
     <t>Female Share of Employment</t>
@@ -3216,6 +3213,9 @@
   <sheetPr/>
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="10.8359375" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="18.09375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -19640,10 +19640,10 @@
     </row>
     <row r="70" spans="1:59">
       <c r="A70" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70" t="s">
         <v>496</v>
-      </c>
-      <c r="B70" t="s">
-        <v>497</v>
       </c>
       <c r="C70" t="s">
         <v>33</v>
@@ -19819,10 +19819,10 @@
     </row>
     <row r="71" spans="1:59">
       <c r="A71" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" t="s">
         <v>496</v>
-      </c>
-      <c r="B71" t="s">
-        <v>497</v>
       </c>
       <c r="C71" t="s">
         <v>34</v>
@@ -19998,10 +19998,10 @@
     </row>
     <row r="72" spans="1:59">
       <c r="A72" t="s">
+        <v>497</v>
+      </c>
+      <c r="B72" t="s">
         <v>498</v>
-      </c>
-      <c r="B72" t="s">
-        <v>499</v>
       </c>
       <c r="C72" t="s">
         <v>33</v>
@@ -20177,10 +20177,10 @@
     </row>
     <row r="73" spans="1:59">
       <c r="A73" t="s">
+        <v>497</v>
+      </c>
+      <c r="B73" t="s">
         <v>498</v>
-      </c>
-      <c r="B73" t="s">
-        <v>499</v>
       </c>
       <c r="C73" t="s">
         <v>34</v>
@@ -20356,10 +20356,10 @@
     </row>
     <row r="74" spans="1:59">
       <c r="A74" t="s">
+        <v>499</v>
+      </c>
+      <c r="B74" t="s">
         <v>500</v>
-      </c>
-      <c r="B74" t="s">
-        <v>501</v>
       </c>
       <c r="C74" t="s">
         <v>33</v>
@@ -20535,10 +20535,10 @@
     </row>
     <row r="75" spans="1:59">
       <c r="A75" t="s">
+        <v>499</v>
+      </c>
+      <c r="B75" t="s">
         <v>500</v>
-      </c>
-      <c r="B75" t="s">
-        <v>501</v>
       </c>
       <c r="C75" t="s">
         <v>34</v>
@@ -20714,10 +20714,10 @@
     </row>
     <row r="76" spans="1:59">
       <c r="A76" t="s">
+        <v>501</v>
+      </c>
+      <c r="B76" t="s">
         <v>502</v>
-      </c>
-      <c r="B76" t="s">
-        <v>503</v>
       </c>
       <c r="C76" t="s">
         <v>33</v>
@@ -20893,10 +20893,10 @@
     </row>
     <row r="77" spans="1:59">
       <c r="A77" t="s">
+        <v>501</v>
+      </c>
+      <c r="B77" t="s">
         <v>502</v>
-      </c>
-      <c r="B77" t="s">
-        <v>503</v>
       </c>
       <c r="C77" t="s">
         <v>34</v>
@@ -21072,10 +21072,10 @@
     </row>
     <row r="78" spans="1:59">
       <c r="A78" t="s">
+        <v>503</v>
+      </c>
+      <c r="B78" t="s">
         <v>504</v>
-      </c>
-      <c r="B78" t="s">
-        <v>505</v>
       </c>
       <c r="C78" t="s">
         <v>33</v>
@@ -21251,10 +21251,10 @@
     </row>
     <row r="79" spans="1:59">
       <c r="A79" t="s">
+        <v>503</v>
+      </c>
+      <c r="B79" t="s">
         <v>504</v>
-      </c>
-      <c r="B79" t="s">
-        <v>505</v>
       </c>
       <c r="C79" t="s">
         <v>34</v>
@@ -21430,7 +21430,7 @@
     </row>
     <row r="80" spans="1:59">
       <c r="A80" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B80" t="s">
         <v>332</v>
@@ -21609,7 +21609,7 @@
     </row>
     <row r="81" spans="1:59">
       <c r="A81" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B81" t="s">
         <v>332</v>
@@ -21788,10 +21788,10 @@
     </row>
     <row r="82" spans="1:59">
       <c r="A82" t="s">
+        <v>506</v>
+      </c>
+      <c r="B82" t="s">
         <v>507</v>
-      </c>
-      <c r="B82" t="s">
-        <v>508</v>
       </c>
       <c r="C82" t="s">
         <v>33</v>
@@ -21967,10 +21967,10 @@
     </row>
     <row r="83" spans="1:59">
       <c r="A83" t="s">
+        <v>506</v>
+      </c>
+      <c r="B83" t="s">
         <v>507</v>
-      </c>
-      <c r="B83" t="s">
-        <v>508</v>
       </c>
       <c r="C83" t="s">
         <v>34</v>
@@ -22146,10 +22146,10 @@
     </row>
     <row r="84" spans="1:59">
       <c r="A84" t="s">
+        <v>508</v>
+      </c>
+      <c r="B84" t="s">
         <v>509</v>
-      </c>
-      <c r="B84" t="s">
-        <v>510</v>
       </c>
       <c r="C84" t="s">
         <v>33</v>
@@ -22325,10 +22325,10 @@
     </row>
     <row r="85" spans="1:59">
       <c r="A85" t="s">
+        <v>508</v>
+      </c>
+      <c r="B85" t="s">
         <v>509</v>
-      </c>
-      <c r="B85" t="s">
-        <v>510</v>
       </c>
       <c r="C85" t="s">
         <v>34</v>
@@ -22504,7 +22504,7 @@
     </row>
     <row r="86" spans="1:59">
       <c r="A86" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B86" t="s">
         <v>346</v>
@@ -22683,7 +22683,7 @@
     </row>
     <row r="87" spans="1:59">
       <c r="A87" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B87" t="s">
         <v>346</v>
@@ -22862,10 +22862,10 @@
     </row>
     <row r="88" spans="1:59">
       <c r="A88" t="s">
+        <v>511</v>
+      </c>
+      <c r="B88" t="s">
         <v>512</v>
-      </c>
-      <c r="B88" t="s">
-        <v>513</v>
       </c>
       <c r="C88" t="s">
         <v>33</v>
@@ -23041,10 +23041,10 @@
     </row>
     <row r="89" spans="1:59">
       <c r="A89" t="s">
+        <v>511</v>
+      </c>
+      <c r="B89" t="s">
         <v>512</v>
-      </c>
-      <c r="B89" t="s">
-        <v>513</v>
       </c>
       <c r="C89" t="s">
         <v>34</v>
@@ -23220,10 +23220,10 @@
     </row>
     <row r="90" spans="1:59">
       <c r="A90" t="s">
+        <v>513</v>
+      </c>
+      <c r="B90" t="s">
         <v>514</v>
-      </c>
-      <c r="B90" t="s">
-        <v>515</v>
       </c>
       <c r="C90" t="s">
         <v>33</v>
@@ -23399,10 +23399,10 @@
     </row>
     <row r="91" spans="1:59">
       <c r="A91" t="s">
+        <v>513</v>
+      </c>
+      <c r="B91" t="s">
         <v>514</v>
-      </c>
-      <c r="B91" t="s">
-        <v>515</v>
       </c>
       <c r="C91" t="s">
         <v>34</v>
@@ -23578,10 +23578,10 @@
     </row>
     <row r="92" spans="1:59">
       <c r="A92" t="s">
+        <v>515</v>
+      </c>
+      <c r="B92" t="s">
         <v>516</v>
-      </c>
-      <c r="B92" t="s">
-        <v>517</v>
       </c>
       <c r="C92" t="s">
         <v>33</v>
@@ -23757,10 +23757,10 @@
     </row>
     <row r="93" spans="1:59">
       <c r="A93" t="s">
+        <v>515</v>
+      </c>
+      <c r="B93" t="s">
         <v>516</v>
-      </c>
-      <c r="B93" t="s">
-        <v>517</v>
       </c>
       <c r="C93" t="s">
         <v>34</v>
@@ -23936,10 +23936,10 @@
     </row>
     <row r="94" spans="1:59">
       <c r="A94" t="s">
+        <v>517</v>
+      </c>
+      <c r="B94" t="s">
         <v>518</v>
-      </c>
-      <c r="B94" t="s">
-        <v>519</v>
       </c>
       <c r="C94" t="s">
         <v>33</v>
@@ -24115,10 +24115,10 @@
     </row>
     <row r="95" spans="1:59">
       <c r="A95" t="s">
+        <v>517</v>
+      </c>
+      <c r="B95" t="s">
         <v>518</v>
-      </c>
-      <c r="B95" t="s">
-        <v>519</v>
       </c>
       <c r="C95" t="s">
         <v>34</v>
@@ -24294,10 +24294,10 @@
     </row>
     <row r="96" spans="1:59">
       <c r="A96" t="s">
+        <v>519</v>
+      </c>
+      <c r="B96" t="s">
         <v>520</v>
-      </c>
-      <c r="B96" t="s">
-        <v>521</v>
       </c>
       <c r="C96" t="s">
         <v>33</v>
@@ -24473,10 +24473,10 @@
     </row>
     <row r="97" spans="1:59">
       <c r="A97" t="s">
+        <v>519</v>
+      </c>
+      <c r="B97" t="s">
         <v>520</v>
-      </c>
-      <c r="B97" t="s">
-        <v>521</v>
       </c>
       <c r="C97" t="s">
         <v>34</v>
@@ -24652,7 +24652,7 @@
     </row>
     <row r="98" spans="1:59">
       <c r="A98" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B98" t="s">
         <v>360</v>
@@ -24831,7 +24831,7 @@
     </row>
     <row r="99" spans="1:59">
       <c r="A99" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B99" t="s">
         <v>360</v>
@@ -25010,10 +25010,10 @@
     </row>
     <row r="100" spans="1:59">
       <c r="A100" t="s">
+        <v>522</v>
+      </c>
+      <c r="B100" t="s">
         <v>523</v>
-      </c>
-      <c r="B100" t="s">
-        <v>524</v>
       </c>
       <c r="C100" t="s">
         <v>33</v>
@@ -25189,10 +25189,10 @@
     </row>
     <row r="101" spans="1:59">
       <c r="A101" t="s">
+        <v>522</v>
+      </c>
+      <c r="B101" t="s">
         <v>523</v>
-      </c>
-      <c r="B101" t="s">
-        <v>524</v>
       </c>
       <c r="C101" t="s">
         <v>34</v>
@@ -25368,10 +25368,10 @@
     </row>
     <row r="102" spans="1:59">
       <c r="A102" t="s">
+        <v>524</v>
+      </c>
+      <c r="B102" t="s">
         <v>525</v>
-      </c>
-      <c r="B102" t="s">
-        <v>526</v>
       </c>
       <c r="C102" t="s">
         <v>33</v>
@@ -25547,10 +25547,10 @@
     </row>
     <row r="103" spans="1:59">
       <c r="A103" t="s">
+        <v>524</v>
+      </c>
+      <c r="B103" t="s">
         <v>525</v>
-      </c>
-      <c r="B103" t="s">
-        <v>526</v>
       </c>
       <c r="C103" t="s">
         <v>34</v>
@@ -25726,7 +25726,7 @@
     </row>
     <row r="104" spans="1:59">
       <c r="A104" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B104" t="s">
         <v>368</v>
@@ -25905,7 +25905,7 @@
     </row>
     <row r="105" spans="1:59">
       <c r="A105" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B105" t="s">
         <v>368</v>
@@ -26084,7 +26084,7 @@
     </row>
     <row r="106" spans="1:59">
       <c r="A106" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B106" t="s">
         <v>370</v>
@@ -26263,7 +26263,7 @@
     </row>
     <row r="107" spans="1:59">
       <c r="A107" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B107" t="s">
         <v>370</v>
@@ -26442,7 +26442,7 @@
     </row>
     <row r="108" spans="1:59">
       <c r="A108" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B108" t="s">
         <v>372</v>
@@ -26621,7 +26621,7 @@
     </row>
     <row r="109" spans="1:59">
       <c r="A109" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B109" t="s">
         <v>372</v>
@@ -26800,10 +26800,10 @@
     </row>
     <row r="110" spans="1:59">
       <c r="A110" t="s">
+        <v>529</v>
+      </c>
+      <c r="B110" t="s">
         <v>530</v>
-      </c>
-      <c r="B110" t="s">
-        <v>531</v>
       </c>
       <c r="C110" t="s">
         <v>33</v>
@@ -26979,10 +26979,10 @@
     </row>
     <row r="111" spans="1:59">
       <c r="A111" t="s">
+        <v>529</v>
+      </c>
+      <c r="B111" t="s">
         <v>530</v>
-      </c>
-      <c r="B111" t="s">
-        <v>531</v>
       </c>
       <c r="C111" t="s">
         <v>34</v>
@@ -27158,10 +27158,10 @@
     </row>
     <row r="112" spans="1:59">
       <c r="A112" t="s">
+        <v>531</v>
+      </c>
+      <c r="B112" t="s">
         <v>532</v>
-      </c>
-      <c r="B112" t="s">
-        <v>533</v>
       </c>
       <c r="C112" t="s">
         <v>33</v>
@@ -27337,10 +27337,10 @@
     </row>
     <row r="113" spans="1:59">
       <c r="A113" t="s">
+        <v>531</v>
+      </c>
+      <c r="B113" t="s">
         <v>532</v>
-      </c>
-      <c r="B113" t="s">
-        <v>533</v>
       </c>
       <c r="C113" t="s">
         <v>34</v>
@@ -27529,336 +27529,336 @@
   <sheetData>
     <row r="1" spans="1:109">
       <c r="A1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B1" t="s">
         <v>534</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>535</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>536</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>537</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>538</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>539</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>540</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>541</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>542</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>543</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>544</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>545</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>546</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>547</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>548</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>549</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>550</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>551</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>552</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>553</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>554</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>555</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>556</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>557</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>558</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>559</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>560</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>561</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>562</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>563</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>564</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>565</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>566</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>567</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>568</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>569</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>570</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>571</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>572</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>573</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>574</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>575</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>576</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>577</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>578</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>579</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>580</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>581</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>582</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>583</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>584</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>585</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>586</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>587</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>588</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>589</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>590</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>591</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>592</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>593</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>594</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>595</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>596</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>597</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>598</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>599</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>600</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>601</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>602</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>603</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>604</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>605</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>606</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>607</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>608</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>609</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>610</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>611</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>612</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>613</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>614</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>615</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>616</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>617</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>618</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>619</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
         <v>620</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CK1" t="s">
         <v>621</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>622</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>623</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>624</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>625</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
         <v>626</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CQ1" t="s">
         <v>627</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>628</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>629</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>630</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>631</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>632</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>633</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>634</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>635</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>636</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>637</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>638</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>639</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>640</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>641</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="2" spans="1:109">
       <c r="A2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B2">
         <v>0.0402201558538603</v>
@@ -28187,7 +28187,7 @@
     </row>
     <row r="3" spans="1:109">
       <c r="A3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B3">
         <v>9.82982932234638e-5</v>
@@ -28516,7 +28516,7 @@
     </row>
     <row r="4" spans="1:109">
       <c r="A4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B4">
         <v>0.000409250734444172</v>
@@ -28845,7 +28845,7 @@
     </row>
     <row r="5" spans="1:109">
       <c r="A5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B5">
         <v>5.45259292703703e-6</v>
@@ -29174,7 +29174,7 @@
     </row>
     <row r="6" spans="1:109">
       <c r="A6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B6">
         <v>0.000975681711948831</v>
@@ -29503,7 +29503,7 @@
     </row>
     <row r="7" spans="1:109">
       <c r="A7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B7">
         <v>0.00114369940762915</v>
@@ -29832,7 +29832,7 @@
     </row>
     <row r="8" spans="1:109">
       <c r="A8" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B8">
         <v>0.000268658093454781</v>
@@ -30161,7 +30161,7 @@
     </row>
     <row r="9" spans="1:109">
       <c r="A9" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B9">
         <v>0.000160319506519733</v>
@@ -30490,7 +30490,7 @@
     </row>
     <row r="10" spans="1:109">
       <c r="A10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B10">
         <v>3.73998941852317e-5</v>
@@ -30819,7 +30819,7 @@
     </row>
     <row r="11" spans="1:109">
       <c r="A11" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B11">
         <v>0.00169721331590622</v>
@@ -31148,7 +31148,7 @@
     </row>
     <row r="12" spans="1:109">
       <c r="A12" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B12">
         <v>0.00216900146083015</v>
@@ -31477,7 +31477,7 @@
     </row>
     <row r="13" spans="1:109">
       <c r="A13" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B13">
         <v>0.000934469634245042</v>
@@ -31806,7 +31806,7 @@
     </row>
     <row r="14" spans="1:109">
       <c r="A14" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B14">
         <v>2.4354966486466e-5</v>
@@ -32135,7 +32135,7 @@
     </row>
     <row r="15" spans="1:109">
       <c r="A15" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B15">
         <v>2.25868530080168e-5</v>
@@ -32464,7 +32464,7 @@
     </row>
     <row r="16" spans="1:109">
       <c r="A16" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B16">
         <v>0.00261136817648139</v>
@@ -32793,7 +32793,7 @@
     </row>
     <row r="17" spans="1:109">
       <c r="A17" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B17">
         <v>0.0256283070734763</v>
@@ -33122,7 +33122,7 @@
     </row>
     <row r="18" spans="1:109">
       <c r="A18" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B18">
         <v>0.000785424101657037</v>
@@ -33451,7 +33451,7 @@
     </row>
     <row r="19" spans="1:109">
       <c r="A19" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B19">
         <v>0.000224973030191175</v>
@@ -33780,7 +33780,7 @@
     </row>
     <row r="20" spans="1:109">
       <c r="A20" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B20">
         <v>0.0250970023115792</v>
@@ -34109,7 +34109,7 @@
     </row>
     <row r="21" spans="1:109">
       <c r="A21" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B21">
         <v>0.00539800969948872</v>
@@ -34438,7 +34438,7 @@
     </row>
     <row r="22" spans="1:109">
       <c r="A22" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B22">
         <v>0.00207471871514707</v>
@@ -34767,7 +34767,7 @@
     </row>
     <row r="23" spans="1:109">
       <c r="A23" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B23">
         <v>0.000894209582588584</v>
@@ -35096,7 +35096,7 @@
     </row>
     <row r="24" spans="1:109">
       <c r="A24" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B24">
         <v>0.00121160479032537</v>
@@ -35425,7 +35425,7 @@
     </row>
     <row r="25" spans="1:109">
       <c r="A25" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B25">
         <v>0.000287360776515488</v>
@@ -35754,7 +35754,7 @@
     </row>
     <row r="26" spans="1:109">
       <c r="A26" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B26">
         <v>7.1391069420014e-5</v>
@@ -36083,7 +36083,7 @@
     </row>
     <row r="27" spans="1:109">
       <c r="A27" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B27">
         <v>0.00111143229736134</v>
@@ -36412,7 +36412,7 @@
     </row>
     <row r="28" spans="1:109">
       <c r="A28" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B28">
         <v>0.000539836661370824</v>
@@ -36741,7 +36741,7 @@
     </row>
     <row r="29" spans="1:109">
       <c r="A29" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B29">
         <v>0.0373778693712526</v>
@@ -37070,7 +37070,7 @@
     </row>
     <row r="30" spans="1:109">
       <c r="A30" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B30">
         <v>0.00213936774847466</v>
@@ -37399,7 +37399,7 @@
     </row>
     <row r="31" spans="1:109">
       <c r="A31" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B31">
         <v>0.000225411884200646</v>
@@ -37728,7 +37728,7 @@
     </row>
     <row r="32" spans="1:109">
       <c r="A32" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B32">
         <v>0.0107713309393064</v>
@@ -38057,7 +38057,7 @@
     </row>
     <row r="33" spans="1:109">
       <c r="A33" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B33">
         <v>0.00218818783891849</v>
@@ -38386,7 +38386,7 @@
     </row>
     <row r="34" spans="1:109">
       <c r="A34" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B34">
         <v>0.00540754519222196</v>
@@ -38715,7 +38715,7 @@
     </row>
     <row r="35" spans="1:109">
       <c r="A35" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B35">
         <v>0.0037255678561969</v>
@@ -39044,7 +39044,7 @@
     </row>
     <row r="36" spans="1:109">
       <c r="A36" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B36">
         <v>0.0073258508849919</v>
@@ -39373,7 +39373,7 @@
     </row>
     <row r="37" spans="1:109">
       <c r="A37" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B37">
         <v>0.0136333189584511</v>
@@ -39702,7 +39702,7 @@
     </row>
     <row r="38" spans="1:109">
       <c r="A38" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B38">
         <v>1.85002397647086e-5</v>
@@ -40031,7 +40031,7 @@
     </row>
     <row r="39" spans="1:109">
       <c r="A39" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B39">
         <v>0.00544075078844532</v>
@@ -40360,7 +40360,7 @@
     </row>
     <row r="40" spans="1:109">
       <c r="A40" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B40">
         <v>0.00325948644861042</v>
@@ -40689,7 +40689,7 @@
     </row>
     <row r="41" spans="1:109">
       <c r="A41" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B41">
         <v>0.034313579057185</v>
@@ -41018,7 +41018,7 @@
     </row>
     <row r="42" spans="1:109">
       <c r="A42" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B42">
         <v>0.00110948713248051</v>
@@ -41347,7 +41347,7 @@
     </row>
     <row r="43" spans="1:109">
       <c r="A43" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B43">
         <v>0.0165050990816206</v>
@@ -41676,7 +41676,7 @@
     </row>
     <row r="44" spans="1:109">
       <c r="A44" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B44">
         <v>0.0579018909774811</v>
@@ -42005,7 +42005,7 @@
     </row>
     <row r="45" spans="1:109">
       <c r="A45" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B45">
         <v>0.00269779243506487</v>
@@ -42334,7 +42334,7 @@
     </row>
     <row r="46" spans="1:109">
       <c r="A46" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B46">
         <v>0.00610160792741824</v>
@@ -42663,7 +42663,7 @@
     </row>
     <row r="47" spans="1:109">
       <c r="A47" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B47">
         <v>0.00131595941740598</v>
@@ -42992,7 +42992,7 @@
     </row>
     <row r="48" spans="1:109">
       <c r="A48" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B48">
         <v>0.00195854755570321</v>
@@ -43321,7 +43321,7 @@
     </row>
     <row r="49" spans="1:109">
       <c r="A49" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B49">
         <v>0.00079313677593296</v>
@@ -43650,7 +43650,7 @@
     </row>
     <row r="50" spans="1:109">
       <c r="A50" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B50">
         <v>0.000198091518108851</v>
@@ -43979,7 +43979,7 @@
     </row>
     <row r="51" spans="1:109">
       <c r="A51" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B51">
         <v>0.00231987985731329</v>
@@ -44308,7 +44308,7 @@
     </row>
     <row r="52" spans="1:109">
       <c r="A52" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B52">
         <v>0.000931328374073347</v>
@@ -44637,7 +44637,7 @@
     </row>
     <row r="53" spans="1:109">
       <c r="A53" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B53">
         <v>0.000364205746723159</v>
@@ -44966,7 +44966,7 @@
     </row>
     <row r="54" spans="1:109">
       <c r="A54" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B54">
         <v>0.000649463904547864</v>
@@ -45295,7 +45295,7 @@
     </row>
     <row r="55" spans="1:109">
       <c r="A55" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B55">
         <v>0.00555786849671755</v>
@@ -45624,7 +45624,7 @@
     </row>
     <row r="56" spans="1:109">
       <c r="A56" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B56">
         <v>0.00490127561548841</v>
@@ -45953,7 +45953,7 @@
     </row>
     <row r="57" spans="1:109">
       <c r="A57" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B57">
         <v>0.000540847616252616</v>
@@ -46282,7 +46282,7 @@
     </row>
     <row r="58" spans="1:109">
       <c r="A58" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B58">
         <v>4.2567492306256e-5</v>
@@ -46611,7 +46611,7 @@
     </row>
     <row r="59" spans="1:109">
       <c r="A59" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B59">
         <v>8.06435934364319e-6</v>
@@ -46940,7 +46940,7 @@
     </row>
     <row r="60" spans="1:109">
       <c r="A60" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B60">
         <v>0.0015421043317966</v>
@@ -47269,7 +47269,7 @@
     </row>
     <row r="61" spans="1:109">
       <c r="A61" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B61">
         <v>0.00116605506911298</v>
@@ -47598,7 +47598,7 @@
     </row>
     <row r="62" spans="1:109">
       <c r="A62" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B62">
         <v>0.000215355826732773</v>
@@ -47927,7 +47927,7 @@
     </row>
     <row r="63" spans="1:109">
       <c r="A63" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B63">
         <v>0.000192942839313473</v>
@@ -48256,7 +48256,7 @@
     </row>
     <row r="64" spans="1:109">
       <c r="A64" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B64">
         <v>1.61933683887383e-5</v>
@@ -48585,7 +48585,7 @@
     </row>
     <row r="65" spans="1:109">
       <c r="A65" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B65">
         <v>0.000502176086744496</v>
@@ -48914,7 +48914,7 @@
     </row>
     <row r="66" spans="1:109">
       <c r="A66" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B66">
         <v>0.000227816780721272</v>
@@ -49243,7 +49243,7 @@
     </row>
     <row r="67" spans="1:109">
       <c r="A67" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B67">
         <v>9.10911540546421e-6</v>
@@ -49572,7 +49572,7 @@
     </row>
     <row r="68" spans="1:109">
       <c r="A68" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B68">
         <v>2.0934037006169e-5</v>
@@ -49901,7 +49901,7 @@
     </row>
     <row r="69" spans="1:109">
       <c r="A69" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B69">
         <v>1.36701638974409e-6</v>
@@ -50230,7 +50230,7 @@
     </row>
     <row r="70" spans="1:109">
       <c r="A70" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B70">
         <v>0.000213669066471902</v>
@@ -50559,7 +50559,7 @@
     </row>
     <row r="71" spans="1:109">
       <c r="A71" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B71">
         <v>0.00441039155888603</v>
@@ -50888,7 +50888,7 @@
     </row>
     <row r="72" spans="1:109">
       <c r="A72" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B72">
         <v>0.000174876650954437</v>
@@ -51217,7 +51217,7 @@
     </row>
     <row r="73" spans="1:109">
       <c r="A73" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B73">
         <v>4.39351266307733e-6</v>
@@ -51546,7 +51546,7 @@
     </row>
     <row r="74" spans="1:109">
       <c r="A74" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B74">
         <v>0.0264810586569319</v>
@@ -51875,7 +51875,7 @@
     </row>
     <row r="75" spans="1:109">
       <c r="A75" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B75">
         <v>0.00070311094400667</v>
@@ -52204,7 +52204,7 @@
     </row>
     <row r="76" spans="1:109">
       <c r="A76" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B76">
         <v>0.000283655142727383</v>
@@ -52533,7 +52533,7 @@
     </row>
     <row r="77" spans="1:109">
       <c r="A77" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B77">
         <v>1.17391623638046e-5</v>
@@ -52862,7 +52862,7 @@
     </row>
     <row r="78" spans="1:109">
       <c r="A78" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B78">
         <v>0.000148053338712109</v>
@@ -53191,7 +53191,7 @@
     </row>
     <row r="79" spans="1:109">
       <c r="A79" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B79">
         <v>2.51477088184212e-5</v>
@@ -53520,7 +53520,7 @@
     </row>
     <row r="80" spans="1:109">
       <c r="A80" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B80">
         <v>3.82019061497735e-7</v>
@@ -53849,7 +53849,7 @@
     </row>
     <row r="81" spans="1:109">
       <c r="A81" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B81">
         <v>0.000202738107078288</v>
@@ -54178,7 +54178,7 @@
     </row>
     <row r="82" spans="1:109">
       <c r="A82" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B82">
         <v>4.26434924280506e-6</v>
@@ -54507,7 +54507,7 @@
     </row>
     <row r="83" spans="1:109">
       <c r="A83" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B83">
         <v>0.00662550190177915</v>
@@ -54836,7 +54836,7 @@
     </row>
     <row r="84" spans="1:109">
       <c r="A84" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B84">
         <v>0.000254531542100205</v>
@@ -55165,7 +55165,7 @@
     </row>
     <row r="85" spans="1:109">
       <c r="A85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B85">
         <v>2.04049226189613e-5</v>
@@ -55494,7 +55494,7 @@
     </row>
     <row r="86" spans="1:109">
       <c r="A86" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B86">
         <v>9.02848881627157e-5</v>
@@ -55823,7 +55823,7 @@
     </row>
     <row r="87" spans="1:109">
       <c r="A87" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B87">
         <v>2.18559134410227e-5</v>
@@ -56152,7 +56152,7 @@
     </row>
     <row r="88" spans="1:109">
       <c r="A88" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B88">
         <v>6.99255827298333e-5</v>
@@ -56481,7 +56481,7 @@
     </row>
     <row r="89" spans="1:109">
       <c r="A89" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B89">
         <v>3.48297180957509e-5</v>
@@ -56810,7 +56810,7 @@
     </row>
     <row r="90" spans="1:109">
       <c r="A90" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B90">
         <v>2.44192333130066e-5</v>
@@ -57139,7 +57139,7 @@
     </row>
     <row r="91" spans="1:109">
       <c r="A91" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B91">
         <v>0.000189641441848841</v>
@@ -57468,7 +57468,7 @@
     </row>
     <row r="92" spans="1:109">
       <c r="A92" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B92">
         <v>3.0509245283073e-8</v>
@@ -57797,7 +57797,7 @@
     </row>
     <row r="93" spans="1:109">
       <c r="A93" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B93">
         <v>0.000189896730033697</v>
@@ -58126,7 +58126,7 @@
     </row>
     <row r="94" spans="1:109">
       <c r="A94" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B94">
         <v>6.65066287599774e-5</v>
@@ -58455,7 +58455,7 @@
     </row>
     <row r="95" spans="1:109">
       <c r="A95" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B95">
         <v>0.00104977855233021</v>
@@ -58784,7 +58784,7 @@
     </row>
     <row r="96" spans="1:109">
       <c r="A96" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B96">
         <v>0.000504954860304928</v>
@@ -59113,7 +59113,7 @@
     </row>
     <row r="97" spans="1:109">
       <c r="A97" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B97">
         <v>0.000719967828004025</v>
@@ -59442,7 +59442,7 @@
     </row>
     <row r="98" spans="1:109">
       <c r="A98" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B98">
         <v>0.00339539924529156</v>
@@ -59771,7 +59771,7 @@
     </row>
     <row r="99" spans="1:109">
       <c r="A99" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B99">
         <v>0.000615692573799323</v>
@@ -60100,7 +60100,7 @@
     </row>
     <row r="100" spans="1:109">
       <c r="A100" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B100">
         <v>0.000179049964173906</v>
@@ -60429,7 +60429,7 @@
     </row>
     <row r="101" spans="1:109">
       <c r="A101" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B101">
         <v>0.000132473226498529</v>
@@ -60758,7 +60758,7 @@
     </row>
     <row r="102" spans="1:109">
       <c r="A102" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B102">
         <v>7.95433199367929e-5</v>
@@ -61087,7 +61087,7 @@
     </row>
     <row r="103" spans="1:109">
       <c r="A103" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B103">
         <v>1.14789404897305e-5</v>
@@ -61416,7 +61416,7 @@
     </row>
     <row r="104" spans="1:109">
       <c r="A104" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B104">
         <v>1.6792019483712e-5</v>
@@ -61745,7 +61745,7 @@
     </row>
     <row r="105" spans="1:109">
       <c r="A105" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B105">
         <v>0.00015818744761855</v>
@@ -62074,7 +62074,7 @@
     </row>
     <row r="106" spans="1:109">
       <c r="A106" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B106">
         <v>4.02173871492111e-5</v>
@@ -62403,7 +62403,7 @@
     </row>
     <row r="107" spans="1:109">
       <c r="A107" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B107">
         <v>3.13991173199815e-5</v>
@@ -62732,7 +62732,7 @@
     </row>
     <row r="108" spans="1:109">
       <c r="A108" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B108">
         <v>0.000264619824447458</v>
@@ -63061,7 +63061,7 @@
     </row>
     <row r="109" spans="1:109">
       <c r="A109" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B109">
         <v>2.86997331704163e-5</v>
@@ -63408,336 +63408,336 @@
   <sheetData>
     <row r="1" spans="1:109">
       <c r="A1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B1" t="s">
         <v>534</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>535</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>536</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>537</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>538</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>539</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>540</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>541</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>542</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" t="s">
         <v>545</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>546</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>547</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>548</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>549</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>550</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>551</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>552</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" t="s">
         <v>555</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>556</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>557</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>558</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>559</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>560</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>563</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>564</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>565</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>566</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>567</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>568</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>569</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>570</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>571</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>572</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>573</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>574</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>575</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>576</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>577</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>578</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>579</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>580</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>581</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>582</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>583</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>584</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>585</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>586</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>587</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>588</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>589</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>590</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>591</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>592</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>593</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>594</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>595</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>596</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>597</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>598</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>599</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>600</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>601</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>602</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>603</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>604</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>605</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>606</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>607</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>608</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>609</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>610</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>611</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>612</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>613</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>614</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>615</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>616</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>617</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>618</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>619</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
         <v>620</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CK1" t="s">
         <v>621</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>622</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>623</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>624</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>625</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
         <v>626</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CQ1" t="s">
         <v>627</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>628</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>629</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>630</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>631</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>632</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>633</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>634</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>635</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>636</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>637</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>638</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>639</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>640</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>641</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="2" spans="1:109">
       <c r="A2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -63766,11 +63766,11 @@
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
-        <v>1.5</v>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -63796,11 +63796,11 @@
       <c r="T2">
         <v>1</v>
       </c>
-      <c r="U2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V2" s="1">
-        <v>1.5</v>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
       </c>
       <c r="W2">
         <v>1</v>
@@ -63820,11 +63820,11 @@
       <c r="AB2">
         <v>1</v>
       </c>
-      <c r="AC2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD2" s="1">
-        <v>1.5</v>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
       </c>
       <c r="AE2">
         <v>1</v>
@@ -64066,7 +64066,7 @@
     </row>
     <row r="3" spans="1:109">
       <c r="A3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -64095,11 +64095,11 @@
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1.5</v>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -64125,11 +64125,11 @@
       <c r="T3">
         <v>1</v>
       </c>
-      <c r="U3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V3" s="1">
-        <v>1.5</v>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
       </c>
       <c r="W3">
         <v>1</v>
@@ -64149,11 +64149,11 @@
       <c r="AB3">
         <v>1</v>
       </c>
-      <c r="AC3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD3" s="1">
-        <v>1.5</v>
+      <c r="AC3">
+        <v>1</v>
+      </c>
+      <c r="AD3">
+        <v>1</v>
       </c>
       <c r="AE3">
         <v>1</v>
@@ -64395,7 +64395,7 @@
     </row>
     <row r="4" spans="1:109">
       <c r="A4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -64424,11 +64424,11 @@
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L4" s="1">
-        <v>1.5</v>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -64454,11 +64454,11 @@
       <c r="T4">
         <v>1</v>
       </c>
-      <c r="U4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V4" s="1">
-        <v>1.5</v>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
       </c>
       <c r="W4">
         <v>1</v>
@@ -64478,11 +64478,11 @@
       <c r="AB4">
         <v>1</v>
       </c>
-      <c r="AC4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD4" s="1">
-        <v>1.5</v>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>1</v>
       </c>
       <c r="AE4">
         <v>1</v>
@@ -64724,7 +64724,7 @@
     </row>
     <row r="5" spans="1:109">
       <c r="A5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -64753,11 +64753,11 @@
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1.5</v>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -64783,11 +64783,11 @@
       <c r="T5">
         <v>1</v>
       </c>
-      <c r="U5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V5" s="1">
-        <v>1.5</v>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
       </c>
       <c r="W5">
         <v>1</v>
@@ -64807,11 +64807,11 @@
       <c r="AB5">
         <v>1</v>
       </c>
-      <c r="AC5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>1.5</v>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
       </c>
       <c r="AE5">
         <v>1</v>
@@ -65053,7 +65053,7 @@
     </row>
     <row r="6" spans="1:109">
       <c r="A6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -65082,11 +65082,11 @@
       <c r="J6">
         <v>1</v>
       </c>
-      <c r="K6" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1.5</v>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -65112,11 +65112,11 @@
       <c r="T6">
         <v>1</v>
       </c>
-      <c r="U6" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V6" s="1">
-        <v>1.5</v>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
       </c>
       <c r="W6">
         <v>1</v>
@@ -65136,11 +65136,11 @@
       <c r="AB6">
         <v>1</v>
       </c>
-      <c r="AC6" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>1.5</v>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
       </c>
       <c r="AE6">
         <v>1</v>
@@ -65382,7 +65382,7 @@
     </row>
     <row r="7" spans="1:109">
       <c r="A7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -65411,11 +65411,11 @@
       <c r="J7">
         <v>1</v>
       </c>
-      <c r="K7" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1.5</v>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
       </c>
       <c r="M7">
         <v>1</v>
@@ -65441,11 +65441,11 @@
       <c r="T7">
         <v>1</v>
       </c>
-      <c r="U7" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V7" s="1">
-        <v>1.5</v>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
       </c>
       <c r="W7">
         <v>1</v>
@@ -65465,11 +65465,11 @@
       <c r="AB7">
         <v>1</v>
       </c>
-      <c r="AC7" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>1.5</v>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
       </c>
       <c r="AE7">
         <v>1</v>
@@ -65711,7 +65711,7 @@
     </row>
     <row r="8" spans="1:109">
       <c r="A8" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -65740,11 +65740,11 @@
       <c r="J8">
         <v>1</v>
       </c>
-      <c r="K8" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1.5</v>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
       </c>
       <c r="M8">
         <v>1</v>
@@ -65770,11 +65770,11 @@
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="U8" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V8" s="1">
-        <v>1.5</v>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
       </c>
       <c r="W8">
         <v>1</v>
@@ -65794,11 +65794,11 @@
       <c r="AB8">
         <v>1</v>
       </c>
-      <c r="AC8" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>1.5</v>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
       </c>
       <c r="AE8">
         <v>1</v>
@@ -66040,7 +66040,7 @@
     </row>
     <row r="9" spans="1:109">
       <c r="A9" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -66069,11 +66069,11 @@
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L9" s="1">
-        <v>1.5</v>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -66099,11 +66099,11 @@
       <c r="T9">
         <v>1</v>
       </c>
-      <c r="U9" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V9" s="1">
-        <v>1.5</v>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
       </c>
       <c r="W9">
         <v>1</v>
@@ -66123,11 +66123,11 @@
       <c r="AB9">
         <v>1</v>
       </c>
-      <c r="AC9" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>1.5</v>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
       </c>
       <c r="AE9">
         <v>1</v>
@@ -66369,7 +66369,7 @@
     </row>
     <row r="10" spans="1:109">
       <c r="A10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -66398,11 +66398,11 @@
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L10" s="1">
-        <v>1.5</v>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
       </c>
       <c r="M10">
         <v>1</v>
@@ -66428,11 +66428,11 @@
       <c r="T10">
         <v>1</v>
       </c>
-      <c r="U10" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V10" s="1">
-        <v>1.5</v>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
       </c>
       <c r="W10">
         <v>1</v>
@@ -66452,11 +66452,11 @@
       <c r="AB10">
         <v>1</v>
       </c>
-      <c r="AC10" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD10" s="1">
-        <v>1.5</v>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
       </c>
       <c r="AE10">
         <v>1</v>
@@ -66698,7 +66698,7 @@
     </row>
     <row r="11" spans="1:109">
       <c r="A11" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -66727,11 +66727,11 @@
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L11" s="1">
-        <v>1.5</v>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -66757,11 +66757,11 @@
       <c r="T11">
         <v>1</v>
       </c>
-      <c r="U11" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V11" s="1">
-        <v>1.5</v>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
       </c>
       <c r="W11">
         <v>1</v>
@@ -66781,11 +66781,11 @@
       <c r="AB11">
         <v>1</v>
       </c>
-      <c r="AC11" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD11" s="1">
-        <v>1.5</v>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
       </c>
       <c r="AE11">
         <v>1</v>
@@ -67027,7 +67027,7 @@
     </row>
     <row r="12" spans="1:109">
       <c r="A12" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -67056,11 +67056,11 @@
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L12" s="1">
-        <v>1.5</v>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
       </c>
       <c r="M12">
         <v>1</v>
@@ -67086,11 +67086,11 @@
       <c r="T12">
         <v>1</v>
       </c>
-      <c r="U12" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V12" s="1">
-        <v>1.5</v>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
       </c>
       <c r="W12">
         <v>1</v>
@@ -67110,11 +67110,11 @@
       <c r="AB12">
         <v>1</v>
       </c>
-      <c r="AC12" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD12" s="1">
-        <v>1.5</v>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AD12">
+        <v>1</v>
       </c>
       <c r="AE12">
         <v>1</v>
@@ -67356,7 +67356,7 @@
     </row>
     <row r="13" spans="1:109">
       <c r="A13" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -67385,11 +67385,11 @@
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L13" s="1">
-        <v>1.5</v>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
       </c>
       <c r="M13">
         <v>1</v>
@@ -67415,11 +67415,11 @@
       <c r="T13">
         <v>1</v>
       </c>
-      <c r="U13" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V13" s="1">
-        <v>1.5</v>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
       </c>
       <c r="W13">
         <v>1</v>
@@ -67439,11 +67439,11 @@
       <c r="AB13">
         <v>1</v>
       </c>
-      <c r="AC13" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD13" s="1">
-        <v>1.5</v>
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AD13">
+        <v>1</v>
       </c>
       <c r="AE13">
         <v>1</v>
@@ -67685,7 +67685,7 @@
     </row>
     <row r="14" spans="1:109">
       <c r="A14" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -67714,11 +67714,11 @@
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L14" s="1">
-        <v>1.5</v>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
       </c>
       <c r="M14">
         <v>1</v>
@@ -67744,11 +67744,11 @@
       <c r="T14">
         <v>1</v>
       </c>
-      <c r="U14" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V14" s="1">
-        <v>1.5</v>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
       </c>
       <c r="W14">
         <v>1</v>
@@ -67768,11 +67768,11 @@
       <c r="AB14">
         <v>1</v>
       </c>
-      <c r="AC14" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD14" s="1">
-        <v>1.5</v>
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
       </c>
       <c r="AE14">
         <v>1</v>
@@ -68014,7 +68014,7 @@
     </row>
     <row r="15" spans="1:109">
       <c r="A15" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -68043,11 +68043,11 @@
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L15" s="1">
-        <v>1.5</v>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
       </c>
       <c r="M15">
         <v>1</v>
@@ -68073,11 +68073,11 @@
       <c r="T15">
         <v>1</v>
       </c>
-      <c r="U15" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V15" s="1">
-        <v>1.5</v>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
       </c>
       <c r="W15">
         <v>1</v>
@@ -68097,11 +68097,11 @@
       <c r="AB15">
         <v>1</v>
       </c>
-      <c r="AC15" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD15" s="1">
-        <v>1.5</v>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
       </c>
       <c r="AE15">
         <v>1</v>
@@ -68343,7 +68343,7 @@
     </row>
     <row r="16" spans="1:109">
       <c r="A16" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -68372,11 +68372,11 @@
       <c r="J16">
         <v>1</v>
       </c>
-      <c r="K16" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L16" s="1">
-        <v>1.5</v>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
       </c>
       <c r="M16">
         <v>1</v>
@@ -68402,11 +68402,11 @@
       <c r="T16">
         <v>1</v>
       </c>
-      <c r="U16" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V16" s="1">
-        <v>1.5</v>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
       </c>
       <c r="W16">
         <v>1</v>
@@ -68426,11 +68426,11 @@
       <c r="AB16">
         <v>1</v>
       </c>
-      <c r="AC16" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD16" s="1">
-        <v>1.5</v>
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AD16">
+        <v>1</v>
       </c>
       <c r="AE16">
         <v>1</v>
@@ -68672,7 +68672,7 @@
     </row>
     <row r="17" spans="1:109">
       <c r="A17" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -68701,11 +68701,11 @@
       <c r="J17">
         <v>1</v>
       </c>
-      <c r="K17" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L17" s="1">
-        <v>1.5</v>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -68731,11 +68731,11 @@
       <c r="T17">
         <v>1</v>
       </c>
-      <c r="U17" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V17" s="1">
-        <v>1.5</v>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
       </c>
       <c r="W17">
         <v>1</v>
@@ -68755,11 +68755,11 @@
       <c r="AB17">
         <v>1</v>
       </c>
-      <c r="AC17" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD17" s="1">
-        <v>1.5</v>
+      <c r="AC17">
+        <v>1</v>
+      </c>
+      <c r="AD17">
+        <v>1</v>
       </c>
       <c r="AE17">
         <v>1</v>
@@ -69001,7 +69001,7 @@
     </row>
     <row r="18" spans="1:109">
       <c r="A18" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -69030,11 +69030,11 @@
       <c r="J18">
         <v>1</v>
       </c>
-      <c r="K18" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L18" s="1">
-        <v>1.5</v>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
       </c>
       <c r="M18">
         <v>1</v>
@@ -69060,11 +69060,11 @@
       <c r="T18">
         <v>1</v>
       </c>
-      <c r="U18" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V18" s="1">
-        <v>1.5</v>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
       </c>
       <c r="W18">
         <v>1</v>
@@ -69084,11 +69084,11 @@
       <c r="AB18">
         <v>1</v>
       </c>
-      <c r="AC18" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD18" s="1">
-        <v>1.5</v>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
       </c>
       <c r="AE18">
         <v>1</v>
@@ -69330,7 +69330,7 @@
     </row>
     <row r="19" spans="1:109">
       <c r="A19" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -69359,11 +69359,11 @@
       <c r="J19">
         <v>1</v>
       </c>
-      <c r="K19" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L19" s="1">
-        <v>1.5</v>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
       </c>
       <c r="M19">
         <v>1</v>
@@ -69389,11 +69389,11 @@
       <c r="T19">
         <v>1</v>
       </c>
-      <c r="U19" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V19" s="1">
-        <v>1.5</v>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
       </c>
       <c r="W19">
         <v>1</v>
@@ -69413,11 +69413,11 @@
       <c r="AB19">
         <v>1</v>
       </c>
-      <c r="AC19" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD19" s="1">
-        <v>1.5</v>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>1</v>
       </c>
       <c r="AE19">
         <v>1</v>
@@ -69659,7 +69659,7 @@
     </row>
     <row r="20" spans="1:109">
       <c r="A20" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -69688,11 +69688,11 @@
       <c r="J20">
         <v>1</v>
       </c>
-      <c r="K20" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L20" s="1">
-        <v>1.5</v>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
       </c>
       <c r="M20">
         <v>1</v>
@@ -69718,11 +69718,11 @@
       <c r="T20">
         <v>1</v>
       </c>
-      <c r="U20" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V20" s="1">
-        <v>1.5</v>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
       </c>
       <c r="W20">
         <v>1</v>
@@ -69742,11 +69742,11 @@
       <c r="AB20">
         <v>1</v>
       </c>
-      <c r="AC20" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD20" s="1">
-        <v>1.5</v>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AD20">
+        <v>1</v>
       </c>
       <c r="AE20">
         <v>1</v>
@@ -69988,7 +69988,7 @@
     </row>
     <row r="21" spans="1:109">
       <c r="A21" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -70017,11 +70017,11 @@
       <c r="J21">
         <v>1</v>
       </c>
-      <c r="K21" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L21" s="1">
-        <v>1.5</v>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
       </c>
       <c r="M21">
         <v>1</v>
@@ -70047,11 +70047,11 @@
       <c r="T21">
         <v>1</v>
       </c>
-      <c r="U21" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V21" s="1">
-        <v>1.5</v>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
       </c>
       <c r="W21">
         <v>1</v>
@@ -70071,11 +70071,11 @@
       <c r="AB21">
         <v>1</v>
       </c>
-      <c r="AC21" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD21" s="1">
-        <v>1.5</v>
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AD21">
+        <v>1</v>
       </c>
       <c r="AE21">
         <v>1</v>
@@ -70317,7 +70317,7 @@
     </row>
     <row r="22" spans="1:109">
       <c r="A22" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -70346,11 +70346,11 @@
       <c r="J22">
         <v>1</v>
       </c>
-      <c r="K22" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L22" s="1">
-        <v>1.5</v>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
       </c>
       <c r="M22">
         <v>1</v>
@@ -70376,11 +70376,11 @@
       <c r="T22">
         <v>1</v>
       </c>
-      <c r="U22" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V22" s="1">
-        <v>1.5</v>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
       </c>
       <c r="W22">
         <v>1</v>
@@ -70400,11 +70400,11 @@
       <c r="AB22">
         <v>1</v>
       </c>
-      <c r="AC22" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD22" s="1">
-        <v>1.5</v>
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
       </c>
       <c r="AE22">
         <v>1</v>
@@ -70646,7 +70646,7 @@
     </row>
     <row r="23" spans="1:109">
       <c r="A23" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -70675,11 +70675,11 @@
       <c r="J23">
         <v>1</v>
       </c>
-      <c r="K23" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L23" s="1">
-        <v>1.5</v>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
       </c>
       <c r="M23">
         <v>1</v>
@@ -70705,11 +70705,11 @@
       <c r="T23">
         <v>1</v>
       </c>
-      <c r="U23" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V23" s="1">
-        <v>1.5</v>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
       </c>
       <c r="W23">
         <v>1</v>
@@ -70729,11 +70729,11 @@
       <c r="AB23">
         <v>1</v>
       </c>
-      <c r="AC23" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD23" s="1">
-        <v>1.5</v>
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AD23">
+        <v>1</v>
       </c>
       <c r="AE23">
         <v>1</v>
@@ -70975,7 +70975,7 @@
     </row>
     <row r="24" spans="1:109">
       <c r="A24" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -71004,11 +71004,11 @@
       <c r="J24">
         <v>1</v>
       </c>
-      <c r="K24" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L24" s="1">
-        <v>1.5</v>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
       </c>
       <c r="M24">
         <v>1</v>
@@ -71034,11 +71034,11 @@
       <c r="T24">
         <v>1</v>
       </c>
-      <c r="U24" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V24" s="1">
-        <v>1.5</v>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
       </c>
       <c r="W24">
         <v>1</v>
@@ -71058,11 +71058,11 @@
       <c r="AB24">
         <v>1</v>
       </c>
-      <c r="AC24" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD24" s="1">
-        <v>1.5</v>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AD24">
+        <v>1</v>
       </c>
       <c r="AE24">
         <v>1</v>
@@ -71304,7 +71304,7 @@
     </row>
     <row r="25" spans="1:109">
       <c r="A25" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -71333,11 +71333,11 @@
       <c r="J25">
         <v>1</v>
       </c>
-      <c r="K25" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L25" s="1">
-        <v>1.5</v>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
       </c>
       <c r="M25">
         <v>1</v>
@@ -71363,11 +71363,11 @@
       <c r="T25">
         <v>1</v>
       </c>
-      <c r="U25" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V25" s="1">
-        <v>1.5</v>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
       </c>
       <c r="W25">
         <v>1</v>
@@ -71387,11 +71387,11 @@
       <c r="AB25">
         <v>1</v>
       </c>
-      <c r="AC25" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD25" s="1">
-        <v>1.5</v>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AD25">
+        <v>1</v>
       </c>
       <c r="AE25">
         <v>1</v>
@@ -71633,7 +71633,7 @@
     </row>
     <row r="26" spans="1:109">
       <c r="A26" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -71662,11 +71662,11 @@
       <c r="J26">
         <v>1</v>
       </c>
-      <c r="K26" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L26" s="1">
-        <v>1.5</v>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
       </c>
       <c r="M26">
         <v>1</v>
@@ -71692,11 +71692,11 @@
       <c r="T26">
         <v>1</v>
       </c>
-      <c r="U26" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V26" s="1">
-        <v>1.5</v>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
       </c>
       <c r="W26">
         <v>1</v>
@@ -71716,11 +71716,11 @@
       <c r="AB26">
         <v>1</v>
       </c>
-      <c r="AC26" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD26" s="1">
-        <v>1.5</v>
+      <c r="AC26">
+        <v>1</v>
+      </c>
+      <c r="AD26">
+        <v>1</v>
       </c>
       <c r="AE26">
         <v>1</v>
@@ -71962,7 +71962,7 @@
     </row>
     <row r="27" spans="1:109">
       <c r="A27" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -71991,11 +71991,11 @@
       <c r="J27">
         <v>1</v>
       </c>
-      <c r="K27" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L27" s="1">
-        <v>1.5</v>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
       </c>
       <c r="M27">
         <v>1</v>
@@ -72021,11 +72021,11 @@
       <c r="T27">
         <v>1</v>
       </c>
-      <c r="U27" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V27" s="1">
-        <v>1.5</v>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27">
+        <v>1</v>
       </c>
       <c r="W27">
         <v>1</v>
@@ -72045,11 +72045,11 @@
       <c r="AB27">
         <v>1</v>
       </c>
-      <c r="AC27" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD27" s="1">
-        <v>1.5</v>
+      <c r="AC27">
+        <v>1</v>
+      </c>
+      <c r="AD27">
+        <v>1</v>
       </c>
       <c r="AE27">
         <v>1</v>
@@ -72291,7 +72291,7 @@
     </row>
     <row r="28" spans="1:109">
       <c r="A28" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -72320,11 +72320,11 @@
       <c r="J28">
         <v>1</v>
       </c>
-      <c r="K28" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L28" s="1">
-        <v>1.5</v>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
       </c>
       <c r="M28">
         <v>1</v>
@@ -72350,11 +72350,11 @@
       <c r="T28">
         <v>1</v>
       </c>
-      <c r="U28" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V28" s="1">
-        <v>1.5</v>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
       </c>
       <c r="W28">
         <v>1</v>
@@ -72374,11 +72374,11 @@
       <c r="AB28">
         <v>1</v>
       </c>
-      <c r="AC28" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD28" s="1">
-        <v>1.5</v>
+      <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AD28">
+        <v>1</v>
       </c>
       <c r="AE28">
         <v>1</v>
@@ -72620,7 +72620,7 @@
     </row>
     <row r="29" spans="1:109">
       <c r="A29" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -72649,11 +72649,11 @@
       <c r="J29">
         <v>1</v>
       </c>
-      <c r="K29" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L29" s="1">
-        <v>1.5</v>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
       </c>
       <c r="M29">
         <v>1</v>
@@ -72679,11 +72679,11 @@
       <c r="T29">
         <v>1</v>
       </c>
-      <c r="U29" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V29" s="1">
-        <v>1.5</v>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29">
+        <v>1</v>
       </c>
       <c r="W29">
         <v>1</v>
@@ -72703,11 +72703,11 @@
       <c r="AB29">
         <v>1</v>
       </c>
-      <c r="AC29" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD29" s="1">
-        <v>1.5</v>
+      <c r="AC29">
+        <v>1</v>
+      </c>
+      <c r="AD29">
+        <v>1</v>
       </c>
       <c r="AE29">
         <v>1</v>
@@ -72949,7 +72949,7 @@
     </row>
     <row r="30" spans="1:109">
       <c r="A30" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -72978,11 +72978,11 @@
       <c r="J30">
         <v>1</v>
       </c>
-      <c r="K30" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L30" s="1">
-        <v>1.5</v>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
       </c>
       <c r="M30">
         <v>1</v>
@@ -73008,11 +73008,11 @@
       <c r="T30">
         <v>1</v>
       </c>
-      <c r="U30" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V30" s="1">
-        <v>1.5</v>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30">
+        <v>1</v>
       </c>
       <c r="W30">
         <v>1</v>
@@ -73032,11 +73032,11 @@
       <c r="AB30">
         <v>1</v>
       </c>
-      <c r="AC30" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD30" s="1">
-        <v>1.5</v>
+      <c r="AC30">
+        <v>1</v>
+      </c>
+      <c r="AD30">
+        <v>1</v>
       </c>
       <c r="AE30">
         <v>1</v>
@@ -73278,7 +73278,7 @@
     </row>
     <row r="31" spans="1:109">
       <c r="A31" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -73307,11 +73307,11 @@
       <c r="J31">
         <v>1</v>
       </c>
-      <c r="K31" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L31" s="1">
-        <v>1.5</v>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
       </c>
       <c r="M31">
         <v>1</v>
@@ -73337,11 +73337,11 @@
       <c r="T31">
         <v>1</v>
       </c>
-      <c r="U31" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V31" s="1">
-        <v>1.5</v>
+      <c r="U31">
+        <v>1</v>
+      </c>
+      <c r="V31">
+        <v>1</v>
       </c>
       <c r="W31">
         <v>1</v>
@@ -73361,11 +73361,11 @@
       <c r="AB31">
         <v>1</v>
       </c>
-      <c r="AC31" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD31" s="1">
-        <v>1.5</v>
+      <c r="AC31">
+        <v>1</v>
+      </c>
+      <c r="AD31">
+        <v>1</v>
       </c>
       <c r="AE31">
         <v>1</v>
@@ -73607,7 +73607,7 @@
     </row>
     <row r="32" spans="1:109">
       <c r="A32" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -73636,11 +73636,11 @@
       <c r="J32">
         <v>1</v>
       </c>
-      <c r="K32" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L32" s="1">
-        <v>1.5</v>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
       </c>
       <c r="M32">
         <v>1</v>
@@ -73666,11 +73666,11 @@
       <c r="T32">
         <v>1</v>
       </c>
-      <c r="U32" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V32" s="1">
-        <v>1.5</v>
+      <c r="U32">
+        <v>1</v>
+      </c>
+      <c r="V32">
+        <v>1</v>
       </c>
       <c r="W32">
         <v>1</v>
@@ -73690,11 +73690,11 @@
       <c r="AB32">
         <v>1</v>
       </c>
-      <c r="AC32" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD32" s="1">
-        <v>1.5</v>
+      <c r="AC32">
+        <v>1</v>
+      </c>
+      <c r="AD32">
+        <v>1</v>
       </c>
       <c r="AE32">
         <v>1</v>
@@ -73936,7 +73936,7 @@
     </row>
     <row r="33" spans="1:109">
       <c r="A33" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -73965,11 +73965,11 @@
       <c r="J33">
         <v>1</v>
       </c>
-      <c r="K33" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L33" s="1">
-        <v>1.5</v>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
       </c>
       <c r="M33">
         <v>1</v>
@@ -73995,11 +73995,11 @@
       <c r="T33">
         <v>1</v>
       </c>
-      <c r="U33" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V33" s="1">
-        <v>1.5</v>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33">
+        <v>1</v>
       </c>
       <c r="W33">
         <v>1</v>
@@ -74019,11 +74019,11 @@
       <c r="AB33">
         <v>1</v>
       </c>
-      <c r="AC33" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD33" s="1">
-        <v>1.5</v>
+      <c r="AC33">
+        <v>1</v>
+      </c>
+      <c r="AD33">
+        <v>1</v>
       </c>
       <c r="AE33">
         <v>1</v>
@@ -74265,7 +74265,7 @@
     </row>
     <row r="34" spans="1:109">
       <c r="A34" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -74294,11 +74294,11 @@
       <c r="J34">
         <v>1</v>
       </c>
-      <c r="K34" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L34" s="1">
-        <v>1.5</v>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
       </c>
       <c r="M34">
         <v>1</v>
@@ -74324,11 +74324,11 @@
       <c r="T34">
         <v>1</v>
       </c>
-      <c r="U34" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V34" s="1">
-        <v>1.5</v>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34">
+        <v>1</v>
       </c>
       <c r="W34">
         <v>1</v>
@@ -74348,11 +74348,11 @@
       <c r="AB34">
         <v>1</v>
       </c>
-      <c r="AC34" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD34" s="1">
-        <v>1.5</v>
+      <c r="AC34">
+        <v>1</v>
+      </c>
+      <c r="AD34">
+        <v>1</v>
       </c>
       <c r="AE34">
         <v>1</v>
@@ -74594,7 +74594,7 @@
     </row>
     <row r="35" spans="1:109">
       <c r="A35" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -74623,11 +74623,11 @@
       <c r="J35">
         <v>1</v>
       </c>
-      <c r="K35" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L35" s="1">
-        <v>1.5</v>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
       </c>
       <c r="M35">
         <v>1</v>
@@ -74653,11 +74653,11 @@
       <c r="T35">
         <v>1</v>
       </c>
-      <c r="U35" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V35" s="1">
-        <v>1.5</v>
+      <c r="U35">
+        <v>1</v>
+      </c>
+      <c r="V35">
+        <v>1</v>
       </c>
       <c r="W35">
         <v>1</v>
@@ -74677,11 +74677,11 @@
       <c r="AB35">
         <v>1</v>
       </c>
-      <c r="AC35" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD35" s="1">
-        <v>1.5</v>
+      <c r="AC35">
+        <v>1</v>
+      </c>
+      <c r="AD35">
+        <v>1</v>
       </c>
       <c r="AE35">
         <v>1</v>
@@ -74923,7 +74923,7 @@
     </row>
     <row r="36" spans="1:109">
       <c r="A36" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -74952,11 +74952,11 @@
       <c r="J36">
         <v>1</v>
       </c>
-      <c r="K36" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L36" s="1">
-        <v>1.5</v>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
       </c>
       <c r="M36">
         <v>1</v>
@@ -74982,11 +74982,11 @@
       <c r="T36">
         <v>1</v>
       </c>
-      <c r="U36" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V36" s="1">
-        <v>1.5</v>
+      <c r="U36">
+        <v>1</v>
+      </c>
+      <c r="V36">
+        <v>1</v>
       </c>
       <c r="W36">
         <v>1</v>
@@ -75006,11 +75006,11 @@
       <c r="AB36">
         <v>1</v>
       </c>
-      <c r="AC36" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD36" s="1">
-        <v>1.5</v>
+      <c r="AC36">
+        <v>1</v>
+      </c>
+      <c r="AD36">
+        <v>1</v>
       </c>
       <c r="AE36">
         <v>1</v>
@@ -75252,7 +75252,7 @@
     </row>
     <row r="37" spans="1:109">
       <c r="A37" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -75281,11 +75281,11 @@
       <c r="J37">
         <v>1</v>
       </c>
-      <c r="K37" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L37" s="1">
-        <v>1.5</v>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
       </c>
       <c r="M37">
         <v>1</v>
@@ -75311,11 +75311,11 @@
       <c r="T37">
         <v>1</v>
       </c>
-      <c r="U37" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V37" s="1">
-        <v>1.5</v>
+      <c r="U37">
+        <v>1</v>
+      </c>
+      <c r="V37">
+        <v>1</v>
       </c>
       <c r="W37">
         <v>1</v>
@@ -75335,11 +75335,11 @@
       <c r="AB37">
         <v>1</v>
       </c>
-      <c r="AC37" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD37" s="1">
-        <v>1.5</v>
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AD37">
+        <v>1</v>
       </c>
       <c r="AE37">
         <v>1</v>
@@ -75581,7 +75581,7 @@
     </row>
     <row r="38" spans="1:109">
       <c r="A38" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -75610,11 +75610,11 @@
       <c r="J38">
         <v>1</v>
       </c>
-      <c r="K38" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L38" s="1">
-        <v>1.5</v>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
       </c>
       <c r="M38">
         <v>1</v>
@@ -75640,11 +75640,11 @@
       <c r="T38">
         <v>1</v>
       </c>
-      <c r="U38" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V38" s="1">
-        <v>1.5</v>
+      <c r="U38">
+        <v>1</v>
+      </c>
+      <c r="V38">
+        <v>1</v>
       </c>
       <c r="W38">
         <v>1</v>
@@ -75664,11 +75664,11 @@
       <c r="AB38">
         <v>1</v>
       </c>
-      <c r="AC38" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="AD38" s="1">
-        <v>1.5</v>
+      <c r="AC38">
+        <v>1</v>
+      </c>
+      <c r="AD38">
+        <v>1</v>
       </c>
       <c r="AE38">
         <v>1</v>
@@ -75910,7 +75910,7 @@
     </row>
     <row r="39" spans="1:109">
       <c r="A39" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -75939,10 +75939,10 @@
       <c r="J39">
         <v>1</v>
       </c>
-      <c r="K39" s="1">
-        <v>1</v>
-      </c>
-      <c r="L39" s="1">
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
         <v>1</v>
       </c>
       <c r="M39">
@@ -75972,7 +75972,7 @@
       <c r="U39">
         <v>1</v>
       </c>
-      <c r="V39" s="1">
+      <c r="V39">
         <v>1</v>
       </c>
       <c r="W39">
@@ -75993,10 +75993,10 @@
       <c r="AB39">
         <v>1</v>
       </c>
-      <c r="AC39" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD39" s="1">
+      <c r="AC39">
+        <v>1</v>
+      </c>
+      <c r="AD39">
         <v>1</v>
       </c>
       <c r="AE39">
@@ -76239,7 +76239,7 @@
     </row>
     <row r="40" spans="1:109">
       <c r="A40" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -76268,10 +76268,10 @@
       <c r="J40">
         <v>1</v>
       </c>
-      <c r="K40" s="1">
-        <v>1</v>
-      </c>
-      <c r="L40" s="1">
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40">
         <v>1</v>
       </c>
       <c r="M40">
@@ -76301,7 +76301,7 @@
       <c r="U40">
         <v>1</v>
       </c>
-      <c r="V40" s="1">
+      <c r="V40">
         <v>1</v>
       </c>
       <c r="W40">
@@ -76322,10 +76322,10 @@
       <c r="AB40">
         <v>1</v>
       </c>
-      <c r="AC40" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD40" s="1">
+      <c r="AC40">
+        <v>1</v>
+      </c>
+      <c r="AD40">
         <v>1</v>
       </c>
       <c r="AE40">
@@ -76568,7 +76568,7 @@
     </row>
     <row r="41" spans="1:109">
       <c r="A41" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -76597,10 +76597,10 @@
       <c r="J41">
         <v>1</v>
       </c>
-      <c r="K41" s="1">
-        <v>1</v>
-      </c>
-      <c r="L41" s="1">
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
         <v>1</v>
       </c>
       <c r="M41">
@@ -76630,7 +76630,7 @@
       <c r="U41">
         <v>1</v>
       </c>
-      <c r="V41" s="1">
+      <c r="V41">
         <v>1</v>
       </c>
       <c r="W41">
@@ -76651,10 +76651,10 @@
       <c r="AB41">
         <v>1</v>
       </c>
-      <c r="AC41" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD41" s="1">
+      <c r="AC41">
+        <v>1</v>
+      </c>
+      <c r="AD41">
         <v>1</v>
       </c>
       <c r="AE41">
@@ -76897,7 +76897,7 @@
     </row>
     <row r="42" spans="1:109">
       <c r="A42" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -76926,10 +76926,10 @@
       <c r="J42">
         <v>1</v>
       </c>
-      <c r="K42" s="1">
-        <v>1</v>
-      </c>
-      <c r="L42" s="1">
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
         <v>1</v>
       </c>
       <c r="M42">
@@ -76959,7 +76959,7 @@
       <c r="U42">
         <v>1</v>
       </c>
-      <c r="V42" s="1">
+      <c r="V42">
         <v>1</v>
       </c>
       <c r="W42">
@@ -76980,10 +76980,10 @@
       <c r="AB42">
         <v>1</v>
       </c>
-      <c r="AC42" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD42" s="1">
+      <c r="AC42">
+        <v>1</v>
+      </c>
+      <c r="AD42">
         <v>1</v>
       </c>
       <c r="AE42">
@@ -77226,7 +77226,7 @@
     </row>
     <row r="43" spans="1:109">
       <c r="A43" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -77255,10 +77255,10 @@
       <c r="J43">
         <v>1</v>
       </c>
-      <c r="K43" s="1">
-        <v>1</v>
-      </c>
-      <c r="L43" s="1">
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43">
         <v>1</v>
       </c>
       <c r="M43">
@@ -77288,7 +77288,7 @@
       <c r="U43">
         <v>1</v>
       </c>
-      <c r="V43" s="1">
+      <c r="V43">
         <v>1</v>
       </c>
       <c r="W43">
@@ -77309,10 +77309,10 @@
       <c r="AB43">
         <v>1</v>
       </c>
-      <c r="AC43" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD43" s="1">
+      <c r="AC43">
+        <v>1</v>
+      </c>
+      <c r="AD43">
         <v>1</v>
       </c>
       <c r="AE43">
@@ -77555,7 +77555,7 @@
     </row>
     <row r="44" spans="1:109">
       <c r="A44" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -77584,10 +77584,10 @@
       <c r="J44">
         <v>1</v>
       </c>
-      <c r="K44" s="1">
-        <v>1</v>
-      </c>
-      <c r="L44" s="1">
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44">
         <v>1</v>
       </c>
       <c r="M44">
@@ -77617,7 +77617,7 @@
       <c r="U44">
         <v>1</v>
       </c>
-      <c r="V44" s="1">
+      <c r="V44">
         <v>1</v>
       </c>
       <c r="W44">
@@ -77638,10 +77638,10 @@
       <c r="AB44">
         <v>1</v>
       </c>
-      <c r="AC44" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD44" s="1">
+      <c r="AC44">
+        <v>1</v>
+      </c>
+      <c r="AD44">
         <v>1</v>
       </c>
       <c r="AE44">
@@ -77884,7 +77884,7 @@
     </row>
     <row r="45" spans="1:109">
       <c r="A45" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -77913,10 +77913,10 @@
       <c r="J45">
         <v>1</v>
       </c>
-      <c r="K45" s="1">
-        <v>1</v>
-      </c>
-      <c r="L45" s="1">
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
         <v>1</v>
       </c>
       <c r="M45">
@@ -77946,7 +77946,7 @@
       <c r="U45">
         <v>1</v>
       </c>
-      <c r="V45" s="1">
+      <c r="V45">
         <v>1</v>
       </c>
       <c r="W45">
@@ -77967,10 +77967,10 @@
       <c r="AB45">
         <v>1</v>
       </c>
-      <c r="AC45" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD45" s="1">
+      <c r="AC45">
+        <v>1</v>
+      </c>
+      <c r="AD45">
         <v>1</v>
       </c>
       <c r="AE45">
@@ -78213,7 +78213,7 @@
     </row>
     <row r="46" spans="1:109">
       <c r="A46" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -78242,10 +78242,10 @@
       <c r="J46">
         <v>1</v>
       </c>
-      <c r="K46" s="1">
-        <v>1</v>
-      </c>
-      <c r="L46" s="1">
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46">
         <v>1</v>
       </c>
       <c r="M46">
@@ -78275,7 +78275,7 @@
       <c r="U46">
         <v>1</v>
       </c>
-      <c r="V46" s="1">
+      <c r="V46">
         <v>1</v>
       </c>
       <c r="W46">
@@ -78296,10 +78296,10 @@
       <c r="AB46">
         <v>1</v>
       </c>
-      <c r="AC46" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD46" s="1">
+      <c r="AC46">
+        <v>1</v>
+      </c>
+      <c r="AD46">
         <v>1</v>
       </c>
       <c r="AE46">
@@ -78542,7 +78542,7 @@
     </row>
     <row r="47" spans="1:109">
       <c r="A47" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -78571,10 +78571,10 @@
       <c r="J47">
         <v>1</v>
       </c>
-      <c r="K47" s="1">
-        <v>1</v>
-      </c>
-      <c r="L47" s="1">
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47">
         <v>1</v>
       </c>
       <c r="M47">
@@ -78604,7 +78604,7 @@
       <c r="U47">
         <v>1</v>
       </c>
-      <c r="V47" s="1">
+      <c r="V47">
         <v>1</v>
       </c>
       <c r="W47">
@@ -78625,10 +78625,10 @@
       <c r="AB47">
         <v>1</v>
       </c>
-      <c r="AC47" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD47" s="1">
+      <c r="AC47">
+        <v>1</v>
+      </c>
+      <c r="AD47">
         <v>1</v>
       </c>
       <c r="AE47">
@@ -78871,7 +78871,7 @@
     </row>
     <row r="48" spans="1:109">
       <c r="A48" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -78900,10 +78900,10 @@
       <c r="J48">
         <v>1</v>
       </c>
-      <c r="K48" s="1">
-        <v>1</v>
-      </c>
-      <c r="L48" s="1">
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48">
         <v>1</v>
       </c>
       <c r="M48">
@@ -78933,7 +78933,7 @@
       <c r="U48">
         <v>1</v>
       </c>
-      <c r="V48" s="1">
+      <c r="V48">
         <v>1</v>
       </c>
       <c r="W48">
@@ -78954,10 +78954,10 @@
       <c r="AB48">
         <v>1</v>
       </c>
-      <c r="AC48" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD48" s="1">
+      <c r="AC48">
+        <v>1</v>
+      </c>
+      <c r="AD48">
         <v>1</v>
       </c>
       <c r="AE48">
@@ -79200,7 +79200,7 @@
     </row>
     <row r="49" spans="1:109">
       <c r="A49" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -79229,10 +79229,10 @@
       <c r="J49">
         <v>1</v>
       </c>
-      <c r="K49" s="1">
-        <v>1</v>
-      </c>
-      <c r="L49" s="1">
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49">
         <v>1</v>
       </c>
       <c r="M49">
@@ -79262,7 +79262,7 @@
       <c r="U49">
         <v>1</v>
       </c>
-      <c r="V49" s="1">
+      <c r="V49">
         <v>1</v>
       </c>
       <c r="W49">
@@ -79283,10 +79283,10 @@
       <c r="AB49">
         <v>1</v>
       </c>
-      <c r="AC49" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD49" s="1">
+      <c r="AC49">
+        <v>1</v>
+      </c>
+      <c r="AD49">
         <v>1</v>
       </c>
       <c r="AE49">
@@ -79529,7 +79529,7 @@
     </row>
     <row r="50" spans="1:109">
       <c r="A50" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -79558,10 +79558,10 @@
       <c r="J50">
         <v>1</v>
       </c>
-      <c r="K50" s="1">
-        <v>1</v>
-      </c>
-      <c r="L50" s="1">
+      <c r="K50">
+        <v>1</v>
+      </c>
+      <c r="L50">
         <v>1</v>
       </c>
       <c r="M50">
@@ -79591,7 +79591,7 @@
       <c r="U50">
         <v>1</v>
       </c>
-      <c r="V50" s="1">
+      <c r="V50">
         <v>1</v>
       </c>
       <c r="W50">
@@ -79612,10 +79612,10 @@
       <c r="AB50">
         <v>1</v>
       </c>
-      <c r="AC50" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD50" s="1">
+      <c r="AC50">
+        <v>1</v>
+      </c>
+      <c r="AD50">
         <v>1</v>
       </c>
       <c r="AE50">
@@ -79858,7 +79858,7 @@
     </row>
     <row r="51" spans="1:109">
       <c r="A51" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -79887,10 +79887,10 @@
       <c r="J51">
         <v>1</v>
       </c>
-      <c r="K51" s="1">
-        <v>1</v>
-      </c>
-      <c r="L51" s="1">
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51">
         <v>1</v>
       </c>
       <c r="M51">
@@ -79920,7 +79920,7 @@
       <c r="U51">
         <v>1</v>
       </c>
-      <c r="V51" s="1">
+      <c r="V51">
         <v>1</v>
       </c>
       <c r="W51">
@@ -79941,10 +79941,10 @@
       <c r="AB51">
         <v>1</v>
       </c>
-      <c r="AC51" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD51" s="1">
+      <c r="AC51">
+        <v>1</v>
+      </c>
+      <c r="AD51">
         <v>1</v>
       </c>
       <c r="AE51">
@@ -80187,7 +80187,7 @@
     </row>
     <row r="52" spans="1:109">
       <c r="A52" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -80216,10 +80216,10 @@
       <c r="J52">
         <v>1</v>
       </c>
-      <c r="K52" s="1">
-        <v>1</v>
-      </c>
-      <c r="L52" s="1">
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52">
         <v>1</v>
       </c>
       <c r="M52">
@@ -80249,7 +80249,7 @@
       <c r="U52">
         <v>1</v>
       </c>
-      <c r="V52" s="1">
+      <c r="V52">
         <v>1</v>
       </c>
       <c r="W52">
@@ -80270,10 +80270,10 @@
       <c r="AB52">
         <v>1</v>
       </c>
-      <c r="AC52" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD52" s="1">
+      <c r="AC52">
+        <v>1</v>
+      </c>
+      <c r="AD52">
         <v>1</v>
       </c>
       <c r="AE52">
@@ -80516,7 +80516,7 @@
     </row>
     <row r="53" spans="1:109">
       <c r="A53" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -80545,10 +80545,10 @@
       <c r="J53">
         <v>1</v>
       </c>
-      <c r="K53" s="1">
-        <v>1</v>
-      </c>
-      <c r="L53" s="1">
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
         <v>1</v>
       </c>
       <c r="M53">
@@ -80578,7 +80578,7 @@
       <c r="U53">
         <v>1</v>
       </c>
-      <c r="V53" s="1">
+      <c r="V53">
         <v>1</v>
       </c>
       <c r="W53">
@@ -80599,10 +80599,10 @@
       <c r="AB53">
         <v>1</v>
       </c>
-      <c r="AC53" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD53" s="1">
+      <c r="AC53">
+        <v>1</v>
+      </c>
+      <c r="AD53">
         <v>1</v>
       </c>
       <c r="AE53">
@@ -80845,7 +80845,7 @@
     </row>
     <row r="54" spans="1:109">
       <c r="A54" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -80874,10 +80874,10 @@
       <c r="J54">
         <v>1</v>
       </c>
-      <c r="K54" s="1">
-        <v>1</v>
-      </c>
-      <c r="L54" s="1">
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54">
         <v>1</v>
       </c>
       <c r="M54">
@@ -80907,7 +80907,7 @@
       <c r="U54">
         <v>1</v>
       </c>
-      <c r="V54" s="1">
+      <c r="V54">
         <v>1</v>
       </c>
       <c r="W54">
@@ -80928,10 +80928,10 @@
       <c r="AB54">
         <v>1</v>
       </c>
-      <c r="AC54" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD54" s="1">
+      <c r="AC54">
+        <v>1</v>
+      </c>
+      <c r="AD54">
         <v>1</v>
       </c>
       <c r="AE54">
@@ -81174,7 +81174,7 @@
     </row>
     <row r="55" spans="1:109">
       <c r="A55" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -81203,10 +81203,10 @@
       <c r="J55">
         <v>1</v>
       </c>
-      <c r="K55" s="1">
-        <v>1</v>
-      </c>
-      <c r="L55" s="1">
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55">
         <v>1</v>
       </c>
       <c r="M55">
@@ -81236,7 +81236,7 @@
       <c r="U55">
         <v>1</v>
       </c>
-      <c r="V55" s="1">
+      <c r="V55">
         <v>1</v>
       </c>
       <c r="W55">
@@ -81257,10 +81257,10 @@
       <c r="AB55">
         <v>1</v>
       </c>
-      <c r="AC55" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD55" s="1">
+      <c r="AC55">
+        <v>1</v>
+      </c>
+      <c r="AD55">
         <v>1</v>
       </c>
       <c r="AE55">
@@ -81503,7 +81503,7 @@
     </row>
     <row r="56" spans="1:109">
       <c r="A56" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -81532,10 +81532,10 @@
       <c r="J56">
         <v>1</v>
       </c>
-      <c r="K56" s="1">
-        <v>1</v>
-      </c>
-      <c r="L56" s="1">
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56">
         <v>1</v>
       </c>
       <c r="M56">
@@ -81565,7 +81565,7 @@
       <c r="U56">
         <v>1</v>
       </c>
-      <c r="V56" s="1">
+      <c r="V56">
         <v>1</v>
       </c>
       <c r="W56">
@@ -81586,10 +81586,10 @@
       <c r="AB56">
         <v>1</v>
       </c>
-      <c r="AC56" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD56" s="1">
+      <c r="AC56">
+        <v>1</v>
+      </c>
+      <c r="AD56">
         <v>1</v>
       </c>
       <c r="AE56">
@@ -81832,7 +81832,7 @@
     </row>
     <row r="57" spans="1:109">
       <c r="A57" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -81861,10 +81861,10 @@
       <c r="J57">
         <v>1</v>
       </c>
-      <c r="K57" s="1">
-        <v>1</v>
-      </c>
-      <c r="L57" s="1">
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="L57">
         <v>1</v>
       </c>
       <c r="M57">
@@ -81894,7 +81894,7 @@
       <c r="U57">
         <v>1</v>
       </c>
-      <c r="V57" s="1">
+      <c r="V57">
         <v>1</v>
       </c>
       <c r="W57">
@@ -81915,10 +81915,10 @@
       <c r="AB57">
         <v>1</v>
       </c>
-      <c r="AC57" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD57" s="1">
+      <c r="AC57">
+        <v>1</v>
+      </c>
+      <c r="AD57">
         <v>1</v>
       </c>
       <c r="AE57">
@@ -82161,7 +82161,7 @@
     </row>
     <row r="58" spans="1:109">
       <c r="A58" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -82190,10 +82190,10 @@
       <c r="J58">
         <v>1</v>
       </c>
-      <c r="K58" s="1">
-        <v>1</v>
-      </c>
-      <c r="L58" s="1">
+      <c r="K58">
+        <v>1</v>
+      </c>
+      <c r="L58">
         <v>1</v>
       </c>
       <c r="M58">
@@ -82223,7 +82223,7 @@
       <c r="U58">
         <v>1</v>
       </c>
-      <c r="V58" s="1">
+      <c r="V58">
         <v>1</v>
       </c>
       <c r="W58">
@@ -82244,10 +82244,10 @@
       <c r="AB58">
         <v>1</v>
       </c>
-      <c r="AC58" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD58" s="1">
+      <c r="AC58">
+        <v>1</v>
+      </c>
+      <c r="AD58">
         <v>1</v>
       </c>
       <c r="AE58">
@@ -82490,7 +82490,7 @@
     </row>
     <row r="59" spans="1:109">
       <c r="A59" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -82519,10 +82519,10 @@
       <c r="J59">
         <v>1</v>
       </c>
-      <c r="K59" s="1">
-        <v>1</v>
-      </c>
-      <c r="L59" s="1">
+      <c r="K59">
+        <v>1</v>
+      </c>
+      <c r="L59">
         <v>1</v>
       </c>
       <c r="M59">
@@ -82552,7 +82552,7 @@
       <c r="U59">
         <v>1</v>
       </c>
-      <c r="V59" s="1">
+      <c r="V59">
         <v>1</v>
       </c>
       <c r="W59">
@@ -82573,10 +82573,10 @@
       <c r="AB59">
         <v>1</v>
       </c>
-      <c r="AC59" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD59" s="1">
+      <c r="AC59">
+        <v>1</v>
+      </c>
+      <c r="AD59">
         <v>1</v>
       </c>
       <c r="AE59">
@@ -82819,7 +82819,7 @@
     </row>
     <row r="60" spans="1:109">
       <c r="A60" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -82848,10 +82848,10 @@
       <c r="J60">
         <v>1</v>
       </c>
-      <c r="K60" s="1">
-        <v>1</v>
-      </c>
-      <c r="L60" s="1">
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60">
         <v>1</v>
       </c>
       <c r="M60">
@@ -82881,7 +82881,7 @@
       <c r="U60">
         <v>1</v>
       </c>
-      <c r="V60" s="1">
+      <c r="V60">
         <v>1</v>
       </c>
       <c r="W60">
@@ -82902,10 +82902,10 @@
       <c r="AB60">
         <v>1</v>
       </c>
-      <c r="AC60" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD60" s="1">
+      <c r="AC60">
+        <v>1</v>
+      </c>
+      <c r="AD60">
         <v>1</v>
       </c>
       <c r="AE60">
@@ -83148,7 +83148,7 @@
     </row>
     <row r="61" spans="1:109">
       <c r="A61" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -83177,10 +83177,10 @@
       <c r="J61">
         <v>1</v>
       </c>
-      <c r="K61" s="1">
-        <v>1</v>
-      </c>
-      <c r="L61" s="1">
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61">
         <v>1</v>
       </c>
       <c r="M61">
@@ -83210,7 +83210,7 @@
       <c r="U61">
         <v>1</v>
       </c>
-      <c r="V61" s="1">
+      <c r="V61">
         <v>1</v>
       </c>
       <c r="W61">
@@ -83231,10 +83231,10 @@
       <c r="AB61">
         <v>1</v>
       </c>
-      <c r="AC61" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD61" s="1">
+      <c r="AC61">
+        <v>1</v>
+      </c>
+      <c r="AD61">
         <v>1</v>
       </c>
       <c r="AE61">
@@ -83477,7 +83477,7 @@
     </row>
     <row r="62" spans="1:109">
       <c r="A62" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -83506,10 +83506,10 @@
       <c r="J62">
         <v>1</v>
       </c>
-      <c r="K62" s="1">
-        <v>1</v>
-      </c>
-      <c r="L62" s="1">
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62">
         <v>1</v>
       </c>
       <c r="M62">
@@ -83539,7 +83539,7 @@
       <c r="U62">
         <v>1</v>
       </c>
-      <c r="V62" s="1">
+      <c r="V62">
         <v>1</v>
       </c>
       <c r="W62">
@@ -83560,10 +83560,10 @@
       <c r="AB62">
         <v>1</v>
       </c>
-      <c r="AC62" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD62" s="1">
+      <c r="AC62">
+        <v>1</v>
+      </c>
+      <c r="AD62">
         <v>1</v>
       </c>
       <c r="AE62">
@@ -83806,7 +83806,7 @@
     </row>
     <row r="63" spans="1:109">
       <c r="A63" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -83835,10 +83835,10 @@
       <c r="J63">
         <v>1</v>
       </c>
-      <c r="K63" s="1">
-        <v>1</v>
-      </c>
-      <c r="L63" s="1">
+      <c r="K63">
+        <v>1</v>
+      </c>
+      <c r="L63">
         <v>1</v>
       </c>
       <c r="M63">
@@ -83868,7 +83868,7 @@
       <c r="U63">
         <v>1</v>
       </c>
-      <c r="V63" s="1">
+      <c r="V63">
         <v>1</v>
       </c>
       <c r="W63">
@@ -83889,10 +83889,10 @@
       <c r="AB63">
         <v>1</v>
       </c>
-      <c r="AC63" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD63" s="1">
+      <c r="AC63">
+        <v>1</v>
+      </c>
+      <c r="AD63">
         <v>1</v>
       </c>
       <c r="AE63">
@@ -84135,7 +84135,7 @@
     </row>
     <row r="64" spans="1:109">
       <c r="A64" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -84164,10 +84164,10 @@
       <c r="J64">
         <v>1</v>
       </c>
-      <c r="K64" s="1">
-        <v>1</v>
-      </c>
-      <c r="L64" s="1">
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64">
         <v>1</v>
       </c>
       <c r="M64">
@@ -84197,7 +84197,7 @@
       <c r="U64">
         <v>1</v>
       </c>
-      <c r="V64" s="1">
+      <c r="V64">
         <v>1</v>
       </c>
       <c r="W64">
@@ -84218,10 +84218,10 @@
       <c r="AB64">
         <v>1</v>
       </c>
-      <c r="AC64" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD64" s="1">
+      <c r="AC64">
+        <v>1</v>
+      </c>
+      <c r="AD64">
         <v>1</v>
       </c>
       <c r="AE64">
@@ -84464,7 +84464,7 @@
     </row>
     <row r="65" spans="1:109">
       <c r="A65" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -84493,10 +84493,10 @@
       <c r="J65">
         <v>1</v>
       </c>
-      <c r="K65" s="1">
-        <v>1</v>
-      </c>
-      <c r="L65" s="1">
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65">
         <v>1</v>
       </c>
       <c r="M65">
@@ -84526,7 +84526,7 @@
       <c r="U65">
         <v>1</v>
       </c>
-      <c r="V65" s="1">
+      <c r="V65">
         <v>1</v>
       </c>
       <c r="W65">
@@ -84547,10 +84547,10 @@
       <c r="AB65">
         <v>1</v>
       </c>
-      <c r="AC65" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD65" s="1">
+      <c r="AC65">
+        <v>1</v>
+      </c>
+      <c r="AD65">
         <v>1</v>
       </c>
       <c r="AE65">
@@ -84793,7 +84793,7 @@
     </row>
     <row r="66" spans="1:109">
       <c r="A66" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -84822,10 +84822,10 @@
       <c r="J66">
         <v>1</v>
       </c>
-      <c r="K66" s="1">
-        <v>1</v>
-      </c>
-      <c r="L66" s="1">
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66">
         <v>1</v>
       </c>
       <c r="M66">
@@ -84855,7 +84855,7 @@
       <c r="U66">
         <v>1</v>
       </c>
-      <c r="V66" s="1">
+      <c r="V66">
         <v>1</v>
       </c>
       <c r="W66">
@@ -84876,10 +84876,10 @@
       <c r="AB66">
         <v>1</v>
       </c>
-      <c r="AC66" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD66" s="1">
+      <c r="AC66">
+        <v>1</v>
+      </c>
+      <c r="AD66">
         <v>1</v>
       </c>
       <c r="AE66">
@@ -85122,7 +85122,7 @@
     </row>
     <row r="67" spans="1:109">
       <c r="A67" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -85151,10 +85151,10 @@
       <c r="J67">
         <v>1</v>
       </c>
-      <c r="K67" s="1">
-        <v>1</v>
-      </c>
-      <c r="L67" s="1">
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67">
         <v>1</v>
       </c>
       <c r="M67">
@@ -85184,7 +85184,7 @@
       <c r="U67">
         <v>1</v>
       </c>
-      <c r="V67" s="1">
+      <c r="V67">
         <v>1</v>
       </c>
       <c r="W67">
@@ -85205,10 +85205,10 @@
       <c r="AB67">
         <v>1</v>
       </c>
-      <c r="AC67" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD67" s="1">
+      <c r="AC67">
+        <v>1</v>
+      </c>
+      <c r="AD67">
         <v>1</v>
       </c>
       <c r="AE67">
@@ -85451,7 +85451,7 @@
     </row>
     <row r="68" spans="1:109">
       <c r="A68" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -85480,10 +85480,10 @@
       <c r="J68">
         <v>1</v>
       </c>
-      <c r="K68" s="1">
-        <v>1</v>
-      </c>
-      <c r="L68" s="1">
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
         <v>1</v>
       </c>
       <c r="M68">
@@ -85513,7 +85513,7 @@
       <c r="U68">
         <v>1</v>
       </c>
-      <c r="V68" s="1">
+      <c r="V68">
         <v>1</v>
       </c>
       <c r="W68">
@@ -85534,10 +85534,10 @@
       <c r="AB68">
         <v>1</v>
       </c>
-      <c r="AC68" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD68" s="1">
+      <c r="AC68">
+        <v>1</v>
+      </c>
+      <c r="AD68">
         <v>1</v>
       </c>
       <c r="AE68">
@@ -85780,7 +85780,7 @@
     </row>
     <row r="69" spans="1:109">
       <c r="A69" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -85809,10 +85809,10 @@
       <c r="J69">
         <v>1</v>
       </c>
-      <c r="K69" s="1">
-        <v>1</v>
-      </c>
-      <c r="L69" s="1">
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69">
         <v>1</v>
       </c>
       <c r="M69">
@@ -85842,7 +85842,7 @@
       <c r="U69">
         <v>1</v>
       </c>
-      <c r="V69" s="1">
+      <c r="V69">
         <v>1</v>
       </c>
       <c r="W69">
@@ -85863,10 +85863,10 @@
       <c r="AB69">
         <v>1</v>
       </c>
-      <c r="AC69" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD69" s="1">
+      <c r="AC69">
+        <v>1</v>
+      </c>
+      <c r="AD69">
         <v>1</v>
       </c>
       <c r="AE69">
@@ -86109,7 +86109,7 @@
     </row>
     <row r="70" spans="1:109">
       <c r="A70" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -86138,10 +86138,10 @@
       <c r="J70">
         <v>1</v>
       </c>
-      <c r="K70" s="1">
-        <v>1</v>
-      </c>
-      <c r="L70" s="1">
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
         <v>1</v>
       </c>
       <c r="M70">
@@ -86171,7 +86171,7 @@
       <c r="U70">
         <v>1</v>
       </c>
-      <c r="V70" s="1">
+      <c r="V70">
         <v>1</v>
       </c>
       <c r="W70">
@@ -86192,10 +86192,10 @@
       <c r="AB70">
         <v>1</v>
       </c>
-      <c r="AC70" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD70" s="1">
+      <c r="AC70">
+        <v>1</v>
+      </c>
+      <c r="AD70">
         <v>1</v>
       </c>
       <c r="AE70">
@@ -86438,7 +86438,7 @@
     </row>
     <row r="71" spans="1:109">
       <c r="A71" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -86467,10 +86467,10 @@
       <c r="J71">
         <v>1</v>
       </c>
-      <c r="K71" s="1">
-        <v>1</v>
-      </c>
-      <c r="L71" s="1">
+      <c r="K71">
+        <v>1</v>
+      </c>
+      <c r="L71">
         <v>1</v>
       </c>
       <c r="M71">
@@ -86500,7 +86500,7 @@
       <c r="U71">
         <v>1</v>
       </c>
-      <c r="V71" s="1">
+      <c r="V71">
         <v>1</v>
       </c>
       <c r="W71">
@@ -86521,10 +86521,10 @@
       <c r="AB71">
         <v>1</v>
       </c>
-      <c r="AC71" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD71" s="1">
+      <c r="AC71">
+        <v>1</v>
+      </c>
+      <c r="AD71">
         <v>1</v>
       </c>
       <c r="AE71">
@@ -86767,7 +86767,7 @@
     </row>
     <row r="72" spans="1:109">
       <c r="A72" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -86796,10 +86796,10 @@
       <c r="J72">
         <v>1</v>
       </c>
-      <c r="K72" s="1">
-        <v>1</v>
-      </c>
-      <c r="L72" s="1">
+      <c r="K72">
+        <v>1</v>
+      </c>
+      <c r="L72">
         <v>1</v>
       </c>
       <c r="M72">
@@ -86829,7 +86829,7 @@
       <c r="U72">
         <v>1</v>
       </c>
-      <c r="V72" s="1">
+      <c r="V72">
         <v>1</v>
       </c>
       <c r="W72">
@@ -86850,10 +86850,10 @@
       <c r="AB72">
         <v>1</v>
       </c>
-      <c r="AC72" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD72" s="1">
+      <c r="AC72">
+        <v>1</v>
+      </c>
+      <c r="AD72">
         <v>1</v>
       </c>
       <c r="AE72">
@@ -87096,7 +87096,7 @@
     </row>
     <row r="73" spans="1:109">
       <c r="A73" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -87125,10 +87125,10 @@
       <c r="J73">
         <v>1</v>
       </c>
-      <c r="K73" s="1">
-        <v>1</v>
-      </c>
-      <c r="L73" s="1">
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73">
         <v>1</v>
       </c>
       <c r="M73">
@@ -87158,7 +87158,7 @@
       <c r="U73">
         <v>1</v>
       </c>
-      <c r="V73" s="1">
+      <c r="V73">
         <v>1</v>
       </c>
       <c r="W73">
@@ -87179,10 +87179,10 @@
       <c r="AB73">
         <v>1</v>
       </c>
-      <c r="AC73" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD73" s="1">
+      <c r="AC73">
+        <v>1</v>
+      </c>
+      <c r="AD73">
         <v>1</v>
       </c>
       <c r="AE73">
@@ -87425,7 +87425,7 @@
     </row>
     <row r="74" spans="1:109">
       <c r="A74" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -87454,10 +87454,10 @@
       <c r="J74">
         <v>1</v>
       </c>
-      <c r="K74" s="1">
-        <v>1</v>
-      </c>
-      <c r="L74" s="1">
+      <c r="K74">
+        <v>1</v>
+      </c>
+      <c r="L74">
         <v>1</v>
       </c>
       <c r="M74">
@@ -87487,7 +87487,7 @@
       <c r="U74">
         <v>1</v>
       </c>
-      <c r="V74" s="1">
+      <c r="V74">
         <v>1</v>
       </c>
       <c r="W74">
@@ -87508,10 +87508,10 @@
       <c r="AB74">
         <v>1</v>
       </c>
-      <c r="AC74" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD74" s="1">
+      <c r="AC74">
+        <v>1</v>
+      </c>
+      <c r="AD74">
         <v>1</v>
       </c>
       <c r="AE74">
@@ -87754,7 +87754,7 @@
     </row>
     <row r="75" spans="1:109">
       <c r="A75" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -87783,10 +87783,10 @@
       <c r="J75">
         <v>1</v>
       </c>
-      <c r="K75" s="1">
-        <v>1</v>
-      </c>
-      <c r="L75" s="1">
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75">
         <v>1</v>
       </c>
       <c r="M75">
@@ -87816,7 +87816,7 @@
       <c r="U75">
         <v>1</v>
       </c>
-      <c r="V75" s="1">
+      <c r="V75">
         <v>1</v>
       </c>
       <c r="W75">
@@ -87837,10 +87837,10 @@
       <c r="AB75">
         <v>1</v>
       </c>
-      <c r="AC75" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD75" s="1">
+      <c r="AC75">
+        <v>1</v>
+      </c>
+      <c r="AD75">
         <v>1</v>
       </c>
       <c r="AE75">
@@ -88083,7 +88083,7 @@
     </row>
     <row r="76" spans="1:109">
       <c r="A76" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -88112,10 +88112,10 @@
       <c r="J76">
         <v>1</v>
       </c>
-      <c r="K76" s="1">
-        <v>1</v>
-      </c>
-      <c r="L76" s="1">
+      <c r="K76">
+        <v>1</v>
+      </c>
+      <c r="L76">
         <v>1</v>
       </c>
       <c r="M76">
@@ -88145,7 +88145,7 @@
       <c r="U76">
         <v>1</v>
       </c>
-      <c r="V76" s="1">
+      <c r="V76">
         <v>1</v>
       </c>
       <c r="W76">
@@ -88166,10 +88166,10 @@
       <c r="AB76">
         <v>1</v>
       </c>
-      <c r="AC76" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD76" s="1">
+      <c r="AC76">
+        <v>1</v>
+      </c>
+      <c r="AD76">
         <v>1</v>
       </c>
       <c r="AE76">
@@ -88412,7 +88412,7 @@
     </row>
     <row r="77" spans="1:109">
       <c r="A77" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -88441,10 +88441,10 @@
       <c r="J77">
         <v>1</v>
       </c>
-      <c r="K77" s="1">
-        <v>1</v>
-      </c>
-      <c r="L77" s="1">
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="L77">
         <v>1</v>
       </c>
       <c r="M77">
@@ -88474,7 +88474,7 @@
       <c r="U77">
         <v>1</v>
       </c>
-      <c r="V77" s="1">
+      <c r="V77">
         <v>1</v>
       </c>
       <c r="W77">
@@ -88495,10 +88495,10 @@
       <c r="AB77">
         <v>1</v>
       </c>
-      <c r="AC77" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD77" s="1">
+      <c r="AC77">
+        <v>1</v>
+      </c>
+      <c r="AD77">
         <v>1</v>
       </c>
       <c r="AE77">
@@ -88741,7 +88741,7 @@
     </row>
     <row r="78" spans="1:109">
       <c r="A78" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -88770,10 +88770,10 @@
       <c r="J78">
         <v>1</v>
       </c>
-      <c r="K78" s="1">
-        <v>1</v>
-      </c>
-      <c r="L78" s="1">
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="L78">
         <v>1</v>
       </c>
       <c r="M78">
@@ -88803,7 +88803,7 @@
       <c r="U78">
         <v>1</v>
       </c>
-      <c r="V78" s="1">
+      <c r="V78">
         <v>1</v>
       </c>
       <c r="W78">
@@ -88824,10 +88824,10 @@
       <c r="AB78">
         <v>1</v>
       </c>
-      <c r="AC78" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD78" s="1">
+      <c r="AC78">
+        <v>1</v>
+      </c>
+      <c r="AD78">
         <v>1</v>
       </c>
       <c r="AE78">
@@ -89070,7 +89070,7 @@
     </row>
     <row r="79" spans="1:109">
       <c r="A79" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -89099,10 +89099,10 @@
       <c r="J79">
         <v>1</v>
       </c>
-      <c r="K79" s="1">
-        <v>1</v>
-      </c>
-      <c r="L79" s="1">
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79">
         <v>1</v>
       </c>
       <c r="M79">
@@ -89132,7 +89132,7 @@
       <c r="U79">
         <v>1</v>
       </c>
-      <c r="V79" s="1">
+      <c r="V79">
         <v>1</v>
       </c>
       <c r="W79">
@@ -89153,10 +89153,10 @@
       <c r="AB79">
         <v>1</v>
       </c>
-      <c r="AC79" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD79" s="1">
+      <c r="AC79">
+        <v>1</v>
+      </c>
+      <c r="AD79">
         <v>1</v>
       </c>
       <c r="AE79">
@@ -89399,7 +89399,7 @@
     </row>
     <row r="80" spans="1:109">
       <c r="A80" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -89428,10 +89428,10 @@
       <c r="J80">
         <v>1</v>
       </c>
-      <c r="K80" s="1">
-        <v>1</v>
-      </c>
-      <c r="L80" s="1">
+      <c r="K80">
+        <v>1</v>
+      </c>
+      <c r="L80">
         <v>1</v>
       </c>
       <c r="M80">
@@ -89461,7 +89461,7 @@
       <c r="U80">
         <v>1</v>
       </c>
-      <c r="V80" s="1">
+      <c r="V80">
         <v>1</v>
       </c>
       <c r="W80">
@@ -89482,10 +89482,10 @@
       <c r="AB80">
         <v>1</v>
       </c>
-      <c r="AC80" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD80" s="1">
+      <c r="AC80">
+        <v>1</v>
+      </c>
+      <c r="AD80">
         <v>1</v>
       </c>
       <c r="AE80">
@@ -89728,7 +89728,7 @@
     </row>
     <row r="81" spans="1:109">
       <c r="A81" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -89757,10 +89757,10 @@
       <c r="J81">
         <v>1</v>
       </c>
-      <c r="K81" s="1">
-        <v>1</v>
-      </c>
-      <c r="L81" s="1">
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="L81">
         <v>1</v>
       </c>
       <c r="M81">
@@ -89790,7 +89790,7 @@
       <c r="U81">
         <v>1</v>
       </c>
-      <c r="V81" s="1">
+      <c r="V81">
         <v>1</v>
       </c>
       <c r="W81">
@@ -89811,10 +89811,10 @@
       <c r="AB81">
         <v>1</v>
       </c>
-      <c r="AC81" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD81" s="1">
+      <c r="AC81">
+        <v>1</v>
+      </c>
+      <c r="AD81">
         <v>1</v>
       </c>
       <c r="AE81">
@@ -90057,7 +90057,7 @@
     </row>
     <row r="82" spans="1:109">
       <c r="A82" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -90086,10 +90086,10 @@
       <c r="J82">
         <v>1</v>
       </c>
-      <c r="K82" s="1">
-        <v>1</v>
-      </c>
-      <c r="L82" s="1">
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
         <v>1</v>
       </c>
       <c r="M82">
@@ -90119,7 +90119,7 @@
       <c r="U82">
         <v>1</v>
       </c>
-      <c r="V82" s="1">
+      <c r="V82">
         <v>1</v>
       </c>
       <c r="W82">
@@ -90140,10 +90140,10 @@
       <c r="AB82">
         <v>1</v>
       </c>
-      <c r="AC82" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD82" s="1">
+      <c r="AC82">
+        <v>1</v>
+      </c>
+      <c r="AD82">
         <v>1</v>
       </c>
       <c r="AE82">
@@ -90386,7 +90386,7 @@
     </row>
     <row r="83" spans="1:109">
       <c r="A83" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -90415,10 +90415,10 @@
       <c r="J83">
         <v>1</v>
       </c>
-      <c r="K83" s="1">
-        <v>1</v>
-      </c>
-      <c r="L83" s="1">
+      <c r="K83">
+        <v>1</v>
+      </c>
+      <c r="L83">
         <v>1</v>
       </c>
       <c r="M83">
@@ -90448,7 +90448,7 @@
       <c r="U83">
         <v>1</v>
       </c>
-      <c r="V83" s="1">
+      <c r="V83">
         <v>1</v>
       </c>
       <c r="W83">
@@ -90469,10 +90469,10 @@
       <c r="AB83">
         <v>1</v>
       </c>
-      <c r="AC83" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD83" s="1">
+      <c r="AC83">
+        <v>1</v>
+      </c>
+      <c r="AD83">
         <v>1</v>
       </c>
       <c r="AE83">
@@ -90715,7 +90715,7 @@
     </row>
     <row r="84" spans="1:109">
       <c r="A84" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -90744,10 +90744,10 @@
       <c r="J84">
         <v>1</v>
       </c>
-      <c r="K84" s="1">
-        <v>1</v>
-      </c>
-      <c r="L84" s="1">
+      <c r="K84">
+        <v>1</v>
+      </c>
+      <c r="L84">
         <v>1</v>
       </c>
       <c r="M84">
@@ -90777,7 +90777,7 @@
       <c r="U84">
         <v>1</v>
       </c>
-      <c r="V84" s="1">
+      <c r="V84">
         <v>1</v>
       </c>
       <c r="W84">
@@ -90798,10 +90798,10 @@
       <c r="AB84">
         <v>1</v>
       </c>
-      <c r="AC84" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD84" s="1">
+      <c r="AC84">
+        <v>1</v>
+      </c>
+      <c r="AD84">
         <v>1</v>
       </c>
       <c r="AE84">
@@ -91044,7 +91044,7 @@
     </row>
     <row r="85" spans="1:109">
       <c r="A85" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -91073,10 +91073,10 @@
       <c r="J85">
         <v>1</v>
       </c>
-      <c r="K85" s="1">
-        <v>1</v>
-      </c>
-      <c r="L85" s="1">
+      <c r="K85">
+        <v>1</v>
+      </c>
+      <c r="L85">
         <v>1</v>
       </c>
       <c r="M85">
@@ -91106,7 +91106,7 @@
       <c r="U85">
         <v>1</v>
       </c>
-      <c r="V85" s="1">
+      <c r="V85">
         <v>1</v>
       </c>
       <c r="W85">
@@ -91127,10 +91127,10 @@
       <c r="AB85">
         <v>1</v>
       </c>
-      <c r="AC85" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD85" s="1">
+      <c r="AC85">
+        <v>1</v>
+      </c>
+      <c r="AD85">
         <v>1</v>
       </c>
       <c r="AE85">
@@ -91373,7 +91373,7 @@
     </row>
     <row r="86" spans="1:109">
       <c r="A86" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -91402,10 +91402,10 @@
       <c r="J86">
         <v>1</v>
       </c>
-      <c r="K86" s="1">
-        <v>1</v>
-      </c>
-      <c r="L86" s="1">
+      <c r="K86">
+        <v>1</v>
+      </c>
+      <c r="L86">
         <v>1</v>
       </c>
       <c r="M86">
@@ -91435,7 +91435,7 @@
       <c r="U86">
         <v>1</v>
       </c>
-      <c r="V86" s="1">
+      <c r="V86">
         <v>1</v>
       </c>
       <c r="W86">
@@ -91456,10 +91456,10 @@
       <c r="AB86">
         <v>1</v>
       </c>
-      <c r="AC86" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD86" s="1">
+      <c r="AC86">
+        <v>1</v>
+      </c>
+      <c r="AD86">
         <v>1</v>
       </c>
       <c r="AE86">
@@ -91702,7 +91702,7 @@
     </row>
     <row r="87" spans="1:109">
       <c r="A87" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -91731,10 +91731,10 @@
       <c r="J87">
         <v>1</v>
       </c>
-      <c r="K87" s="1">
-        <v>1</v>
-      </c>
-      <c r="L87" s="1">
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
         <v>1</v>
       </c>
       <c r="M87">
@@ -91764,7 +91764,7 @@
       <c r="U87">
         <v>1</v>
       </c>
-      <c r="V87" s="1">
+      <c r="V87">
         <v>1</v>
       </c>
       <c r="W87">
@@ -91785,10 +91785,10 @@
       <c r="AB87">
         <v>1</v>
       </c>
-      <c r="AC87" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD87" s="1">
+      <c r="AC87">
+        <v>1</v>
+      </c>
+      <c r="AD87">
         <v>1</v>
       </c>
       <c r="AE87">
@@ -92031,7 +92031,7 @@
     </row>
     <row r="88" spans="1:109">
       <c r="A88" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -92060,10 +92060,10 @@
       <c r="J88">
         <v>1</v>
       </c>
-      <c r="K88" s="1">
-        <v>1</v>
-      </c>
-      <c r="L88" s="1">
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88">
         <v>1</v>
       </c>
       <c r="M88">
@@ -92093,7 +92093,7 @@
       <c r="U88">
         <v>1</v>
       </c>
-      <c r="V88" s="1">
+      <c r="V88">
         <v>1</v>
       </c>
       <c r="W88">
@@ -92114,10 +92114,10 @@
       <c r="AB88">
         <v>1</v>
       </c>
-      <c r="AC88" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD88" s="1">
+      <c r="AC88">
+        <v>1</v>
+      </c>
+      <c r="AD88">
         <v>1</v>
       </c>
       <c r="AE88">
@@ -92360,7 +92360,7 @@
     </row>
     <row r="89" spans="1:109">
       <c r="A89" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -92389,10 +92389,10 @@
       <c r="J89">
         <v>1</v>
       </c>
-      <c r="K89" s="1">
-        <v>1</v>
-      </c>
-      <c r="L89" s="1">
+      <c r="K89">
+        <v>1</v>
+      </c>
+      <c r="L89">
         <v>1</v>
       </c>
       <c r="M89">
@@ -92422,7 +92422,7 @@
       <c r="U89">
         <v>1</v>
       </c>
-      <c r="V89" s="1">
+      <c r="V89">
         <v>1</v>
       </c>
       <c r="W89">
@@ -92443,10 +92443,10 @@
       <c r="AB89">
         <v>1</v>
       </c>
-      <c r="AC89" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD89" s="1">
+      <c r="AC89">
+        <v>1</v>
+      </c>
+      <c r="AD89">
         <v>1</v>
       </c>
       <c r="AE89">
@@ -92689,7 +92689,7 @@
     </row>
     <row r="90" spans="1:109">
       <c r="A90" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -92718,10 +92718,10 @@
       <c r="J90">
         <v>1</v>
       </c>
-      <c r="K90" s="1">
-        <v>1</v>
-      </c>
-      <c r="L90" s="1">
+      <c r="K90">
+        <v>1</v>
+      </c>
+      <c r="L90">
         <v>1</v>
       </c>
       <c r="M90">
@@ -92751,7 +92751,7 @@
       <c r="U90">
         <v>1</v>
       </c>
-      <c r="V90" s="1">
+      <c r="V90">
         <v>1</v>
       </c>
       <c r="W90">
@@ -92772,10 +92772,10 @@
       <c r="AB90">
         <v>1</v>
       </c>
-      <c r="AC90" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD90" s="1">
+      <c r="AC90">
+        <v>1</v>
+      </c>
+      <c r="AD90">
         <v>1</v>
       </c>
       <c r="AE90">
@@ -93018,7 +93018,7 @@
     </row>
     <row r="91" spans="1:109">
       <c r="A91" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -93047,10 +93047,10 @@
       <c r="J91">
         <v>1</v>
       </c>
-      <c r="K91" s="1">
-        <v>1</v>
-      </c>
-      <c r="L91" s="1">
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91">
         <v>1</v>
       </c>
       <c r="M91">
@@ -93080,7 +93080,7 @@
       <c r="U91">
         <v>1</v>
       </c>
-      <c r="V91" s="1">
+      <c r="V91">
         <v>1</v>
       </c>
       <c r="W91">
@@ -93101,10 +93101,10 @@
       <c r="AB91">
         <v>1</v>
       </c>
-      <c r="AC91" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD91" s="1">
+      <c r="AC91">
+        <v>1</v>
+      </c>
+      <c r="AD91">
         <v>1</v>
       </c>
       <c r="AE91">
@@ -93347,7 +93347,7 @@
     </row>
     <row r="92" spans="1:109">
       <c r="A92" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -93376,10 +93376,10 @@
       <c r="J92">
         <v>1</v>
       </c>
-      <c r="K92" s="1">
-        <v>1</v>
-      </c>
-      <c r="L92" s="1">
+      <c r="K92">
+        <v>1</v>
+      </c>
+      <c r="L92">
         <v>1</v>
       </c>
       <c r="M92">
@@ -93409,7 +93409,7 @@
       <c r="U92">
         <v>1</v>
       </c>
-      <c r="V92" s="1">
+      <c r="V92">
         <v>1</v>
       </c>
       <c r="W92">
@@ -93430,10 +93430,10 @@
       <c r="AB92">
         <v>1</v>
       </c>
-      <c r="AC92" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD92" s="1">
+      <c r="AC92">
+        <v>1</v>
+      </c>
+      <c r="AD92">
         <v>1</v>
       </c>
       <c r="AE92">
@@ -93676,7 +93676,7 @@
     </row>
     <row r="93" spans="1:109">
       <c r="A93" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -93705,10 +93705,10 @@
       <c r="J93">
         <v>1</v>
       </c>
-      <c r="K93" s="1">
-        <v>1</v>
-      </c>
-      <c r="L93" s="1">
+      <c r="K93">
+        <v>1</v>
+      </c>
+      <c r="L93">
         <v>1</v>
       </c>
       <c r="M93">
@@ -93738,7 +93738,7 @@
       <c r="U93">
         <v>1</v>
       </c>
-      <c r="V93" s="1">
+      <c r="V93">
         <v>1</v>
       </c>
       <c r="W93">
@@ -93759,10 +93759,10 @@
       <c r="AB93">
         <v>1</v>
       </c>
-      <c r="AC93" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD93" s="1">
+      <c r="AC93">
+        <v>1</v>
+      </c>
+      <c r="AD93">
         <v>1</v>
       </c>
       <c r="AE93">
@@ -94005,7 +94005,7 @@
     </row>
     <row r="94" spans="1:109">
       <c r="A94" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -94034,10 +94034,10 @@
       <c r="J94">
         <v>1</v>
       </c>
-      <c r="K94" s="1">
-        <v>1</v>
-      </c>
-      <c r="L94" s="1">
+      <c r="K94">
+        <v>1</v>
+      </c>
+      <c r="L94">
         <v>1</v>
       </c>
       <c r="M94">
@@ -94067,7 +94067,7 @@
       <c r="U94">
         <v>1</v>
       </c>
-      <c r="V94" s="1">
+      <c r="V94">
         <v>1</v>
       </c>
       <c r="W94">
@@ -94088,10 +94088,10 @@
       <c r="AB94">
         <v>1</v>
       </c>
-      <c r="AC94" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD94" s="1">
+      <c r="AC94">
+        <v>1</v>
+      </c>
+      <c r="AD94">
         <v>1</v>
       </c>
       <c r="AE94">
@@ -94334,7 +94334,7 @@
     </row>
     <row r="95" spans="1:109">
       <c r="A95" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -94363,10 +94363,10 @@
       <c r="J95">
         <v>1</v>
       </c>
-      <c r="K95" s="1">
-        <v>1</v>
-      </c>
-      <c r="L95" s="1">
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="L95">
         <v>1</v>
       </c>
       <c r="M95">
@@ -94396,7 +94396,7 @@
       <c r="U95">
         <v>1</v>
       </c>
-      <c r="V95" s="1">
+      <c r="V95">
         <v>1</v>
       </c>
       <c r="W95">
@@ -94417,10 +94417,10 @@
       <c r="AB95">
         <v>1</v>
       </c>
-      <c r="AC95" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD95" s="1">
+      <c r="AC95">
+        <v>1</v>
+      </c>
+      <c r="AD95">
         <v>1</v>
       </c>
       <c r="AE95">
@@ -94663,7 +94663,7 @@
     </row>
     <row r="96" spans="1:109">
       <c r="A96" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -94692,10 +94692,10 @@
       <c r="J96">
         <v>1</v>
       </c>
-      <c r="K96" s="1">
-        <v>1</v>
-      </c>
-      <c r="L96" s="1">
+      <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="L96">
         <v>1</v>
       </c>
       <c r="M96">
@@ -94725,7 +94725,7 @@
       <c r="U96">
         <v>1</v>
       </c>
-      <c r="V96" s="1">
+      <c r="V96">
         <v>1</v>
       </c>
       <c r="W96">
@@ -94746,10 +94746,10 @@
       <c r="AB96">
         <v>1</v>
       </c>
-      <c r="AC96" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD96" s="1">
+      <c r="AC96">
+        <v>1</v>
+      </c>
+      <c r="AD96">
         <v>1</v>
       </c>
       <c r="AE96">
@@ -94992,7 +94992,7 @@
     </row>
     <row r="97" spans="1:109">
       <c r="A97" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -95021,10 +95021,10 @@
       <c r="J97">
         <v>1</v>
       </c>
-      <c r="K97" s="1">
-        <v>1</v>
-      </c>
-      <c r="L97" s="1">
+      <c r="K97">
+        <v>1</v>
+      </c>
+      <c r="L97">
         <v>1</v>
       </c>
       <c r="M97">
@@ -95054,7 +95054,7 @@
       <c r="U97">
         <v>1</v>
       </c>
-      <c r="V97" s="1">
+      <c r="V97">
         <v>1</v>
       </c>
       <c r="W97">
@@ -95075,10 +95075,10 @@
       <c r="AB97">
         <v>1</v>
       </c>
-      <c r="AC97" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD97" s="1">
+      <c r="AC97">
+        <v>1</v>
+      </c>
+      <c r="AD97">
         <v>1</v>
       </c>
       <c r="AE97">
@@ -95321,7 +95321,7 @@
     </row>
     <row r="98" spans="1:109">
       <c r="A98" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -95350,10 +95350,10 @@
       <c r="J98">
         <v>1</v>
       </c>
-      <c r="K98" s="1">
-        <v>1</v>
-      </c>
-      <c r="L98" s="1">
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
         <v>1</v>
       </c>
       <c r="M98">
@@ -95383,7 +95383,7 @@
       <c r="U98">
         <v>1</v>
       </c>
-      <c r="V98" s="1">
+      <c r="V98">
         <v>1</v>
       </c>
       <c r="W98">
@@ -95404,10 +95404,10 @@
       <c r="AB98">
         <v>1</v>
       </c>
-      <c r="AC98" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD98" s="1">
+      <c r="AC98">
+        <v>1</v>
+      </c>
+      <c r="AD98">
         <v>1</v>
       </c>
       <c r="AE98">
@@ -95650,7 +95650,7 @@
     </row>
     <row r="99" spans="1:109">
       <c r="A99" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -95679,10 +95679,10 @@
       <c r="J99">
         <v>1</v>
       </c>
-      <c r="K99" s="1">
-        <v>1</v>
-      </c>
-      <c r="L99" s="1">
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99">
         <v>1</v>
       </c>
       <c r="M99">
@@ -95712,7 +95712,7 @@
       <c r="U99">
         <v>1</v>
       </c>
-      <c r="V99" s="1">
+      <c r="V99">
         <v>1</v>
       </c>
       <c r="W99">
@@ -95733,10 +95733,10 @@
       <c r="AB99">
         <v>1</v>
       </c>
-      <c r="AC99" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD99" s="1">
+      <c r="AC99">
+        <v>1</v>
+      </c>
+      <c r="AD99">
         <v>1</v>
       </c>
       <c r="AE99">
@@ -95979,7 +95979,7 @@
     </row>
     <row r="100" spans="1:109">
       <c r="A100" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -96008,10 +96008,10 @@
       <c r="J100">
         <v>1</v>
       </c>
-      <c r="K100" s="1">
-        <v>1</v>
-      </c>
-      <c r="L100" s="1">
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
         <v>1</v>
       </c>
       <c r="M100">
@@ -96041,7 +96041,7 @@
       <c r="U100">
         <v>1</v>
       </c>
-      <c r="V100" s="1">
+      <c r="V100">
         <v>1</v>
       </c>
       <c r="W100">
@@ -96062,10 +96062,10 @@
       <c r="AB100">
         <v>1</v>
       </c>
-      <c r="AC100" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD100" s="1">
+      <c r="AC100">
+        <v>1</v>
+      </c>
+      <c r="AD100">
         <v>1</v>
       </c>
       <c r="AE100">
@@ -96308,7 +96308,7 @@
     </row>
     <row r="101" spans="1:109">
       <c r="A101" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -96337,10 +96337,10 @@
       <c r="J101">
         <v>1</v>
       </c>
-      <c r="K101" s="1">
-        <v>1</v>
-      </c>
-      <c r="L101" s="1">
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
         <v>1</v>
       </c>
       <c r="M101">
@@ -96370,7 +96370,7 @@
       <c r="U101">
         <v>1</v>
       </c>
-      <c r="V101" s="1">
+      <c r="V101">
         <v>1</v>
       </c>
       <c r="W101">
@@ -96391,10 +96391,10 @@
       <c r="AB101">
         <v>1</v>
       </c>
-      <c r="AC101" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD101" s="1">
+      <c r="AC101">
+        <v>1</v>
+      </c>
+      <c r="AD101">
         <v>1</v>
       </c>
       <c r="AE101">
@@ -96637,7 +96637,7 @@
     </row>
     <row r="102" spans="1:109">
       <c r="A102" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -96666,10 +96666,10 @@
       <c r="J102">
         <v>1</v>
       </c>
-      <c r="K102" s="1">
-        <v>1</v>
-      </c>
-      <c r="L102" s="1">
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
         <v>1</v>
       </c>
       <c r="M102">
@@ -96699,7 +96699,7 @@
       <c r="U102">
         <v>1</v>
       </c>
-      <c r="V102" s="1">
+      <c r="V102">
         <v>1</v>
       </c>
       <c r="W102">
@@ -96720,10 +96720,10 @@
       <c r="AB102">
         <v>1</v>
       </c>
-      <c r="AC102" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD102" s="1">
+      <c r="AC102">
+        <v>1</v>
+      </c>
+      <c r="AD102">
         <v>1</v>
       </c>
       <c r="AE102">
@@ -96966,7 +96966,7 @@
     </row>
     <row r="103" spans="1:109">
       <c r="A103" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -96995,10 +96995,10 @@
       <c r="J103">
         <v>1</v>
       </c>
-      <c r="K103" s="1">
-        <v>1</v>
-      </c>
-      <c r="L103" s="1">
+      <c r="K103">
+        <v>1</v>
+      </c>
+      <c r="L103">
         <v>1</v>
       </c>
       <c r="M103">
@@ -97028,7 +97028,7 @@
       <c r="U103">
         <v>1</v>
       </c>
-      <c r="V103" s="1">
+      <c r="V103">
         <v>1</v>
       </c>
       <c r="W103">
@@ -97049,10 +97049,10 @@
       <c r="AB103">
         <v>1</v>
       </c>
-      <c r="AC103" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD103" s="1">
+      <c r="AC103">
+        <v>1</v>
+      </c>
+      <c r="AD103">
         <v>1</v>
       </c>
       <c r="AE103">
@@ -97295,7 +97295,7 @@
     </row>
     <row r="104" spans="1:109">
       <c r="A104" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -97324,10 +97324,10 @@
       <c r="J104">
         <v>1</v>
       </c>
-      <c r="K104" s="1">
-        <v>1</v>
-      </c>
-      <c r="L104" s="1">
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
         <v>1</v>
       </c>
       <c r="M104">
@@ -97357,7 +97357,7 @@
       <c r="U104">
         <v>1</v>
       </c>
-      <c r="V104" s="1">
+      <c r="V104">
         <v>1</v>
       </c>
       <c r="W104">
@@ -97378,10 +97378,10 @@
       <c r="AB104">
         <v>1</v>
       </c>
-      <c r="AC104" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD104" s="1">
+      <c r="AC104">
+        <v>1</v>
+      </c>
+      <c r="AD104">
         <v>1</v>
       </c>
       <c r="AE104">
@@ -97624,7 +97624,7 @@
     </row>
     <row r="105" spans="1:109">
       <c r="A105" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -97653,10 +97653,10 @@
       <c r="J105">
         <v>1</v>
       </c>
-      <c r="K105" s="1">
-        <v>1</v>
-      </c>
-      <c r="L105" s="1">
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105">
         <v>1</v>
       </c>
       <c r="M105">
@@ -97686,7 +97686,7 @@
       <c r="U105">
         <v>1</v>
       </c>
-      <c r="V105" s="1">
+      <c r="V105">
         <v>1</v>
       </c>
       <c r="W105">
@@ -97707,10 +97707,10 @@
       <c r="AB105">
         <v>1</v>
       </c>
-      <c r="AC105" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD105" s="1">
+      <c r="AC105">
+        <v>1</v>
+      </c>
+      <c r="AD105">
         <v>1</v>
       </c>
       <c r="AE105">
@@ -97953,7 +97953,7 @@
     </row>
     <row r="106" spans="1:109">
       <c r="A106" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -97982,10 +97982,10 @@
       <c r="J106">
         <v>1</v>
       </c>
-      <c r="K106" s="1">
-        <v>1</v>
-      </c>
-      <c r="L106" s="1">
+      <c r="K106">
+        <v>1</v>
+      </c>
+      <c r="L106">
         <v>1</v>
       </c>
       <c r="M106">
@@ -98015,7 +98015,7 @@
       <c r="U106">
         <v>1</v>
       </c>
-      <c r="V106" s="1">
+      <c r="V106">
         <v>1</v>
       </c>
       <c r="W106">
@@ -98036,10 +98036,10 @@
       <c r="AB106">
         <v>1</v>
       </c>
-      <c r="AC106" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD106" s="1">
+      <c r="AC106">
+        <v>1</v>
+      </c>
+      <c r="AD106">
         <v>1</v>
       </c>
       <c r="AE106">
@@ -98282,7 +98282,7 @@
     </row>
     <row r="107" spans="1:109">
       <c r="A107" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -98311,10 +98311,10 @@
       <c r="J107">
         <v>1</v>
       </c>
-      <c r="K107" s="1">
-        <v>1</v>
-      </c>
-      <c r="L107" s="1">
+      <c r="K107">
+        <v>1</v>
+      </c>
+      <c r="L107">
         <v>1</v>
       </c>
       <c r="M107">
@@ -98344,7 +98344,7 @@
       <c r="U107">
         <v>1</v>
       </c>
-      <c r="V107" s="1">
+      <c r="V107">
         <v>1</v>
       </c>
       <c r="W107">
@@ -98365,10 +98365,10 @@
       <c r="AB107">
         <v>1</v>
       </c>
-      <c r="AC107" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD107" s="1">
+      <c r="AC107">
+        <v>1</v>
+      </c>
+      <c r="AD107">
         <v>1</v>
       </c>
       <c r="AE107">
@@ -98611,7 +98611,7 @@
     </row>
     <row r="108" spans="1:109">
       <c r="A108" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -98640,10 +98640,10 @@
       <c r="J108">
         <v>1</v>
       </c>
-      <c r="K108" s="1">
-        <v>1</v>
-      </c>
-      <c r="L108" s="1">
+      <c r="K108">
+        <v>1</v>
+      </c>
+      <c r="L108">
         <v>1</v>
       </c>
       <c r="M108">
@@ -98673,7 +98673,7 @@
       <c r="U108">
         <v>1</v>
       </c>
-      <c r="V108" s="1">
+      <c r="V108">
         <v>1</v>
       </c>
       <c r="W108">
@@ -98694,10 +98694,10 @@
       <c r="AB108">
         <v>1</v>
       </c>
-      <c r="AC108" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD108" s="1">
+      <c r="AC108">
+        <v>1</v>
+      </c>
+      <c r="AD108">
         <v>1</v>
       </c>
       <c r="AE108">
@@ -98940,7 +98940,7 @@
     </row>
     <row r="109" spans="1:109">
       <c r="A109" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -98969,10 +98969,10 @@
       <c r="J109">
         <v>1</v>
       </c>
-      <c r="K109" s="1">
-        <v>1</v>
-      </c>
-      <c r="L109" s="1">
+      <c r="K109">
+        <v>1</v>
+      </c>
+      <c r="L109">
         <v>1</v>
       </c>
       <c r="M109">
@@ -99002,7 +99002,7 @@
       <c r="U109">
         <v>1</v>
       </c>
-      <c r="V109" s="1">
+      <c r="V109">
         <v>1</v>
       </c>
       <c r="W109">
@@ -99023,10 +99023,10 @@
       <c r="AB109">
         <v>1</v>
       </c>
-      <c r="AC109" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD109" s="1">
+      <c r="AC109">
+        <v>1</v>
+      </c>
+      <c r="AD109">
         <v>1</v>
       </c>
       <c r="AE109">

--- a/data/initial_state_2026.xlsx
+++ b/data/initial_state_2026.xlsx
@@ -3346,7 +3346,7 @@
         <v>24</v>
       </c>
       <c r="C12">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13" spans="1:3">

--- a/data/initial_state_2026.xlsx
+++ b/data/initial_state_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="14540"/>
+    <workbookView windowWidth="30240" windowHeight="14540" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="global.pars" sheetId="1" r:id="rId1"/>
@@ -12534,166 +12534,166 @@
         <v>236</v>
       </c>
       <c r="F30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="G30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="H30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="I30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="J30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="K30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="L30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="M30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="N30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="O30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="P30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="Q30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="R30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="S30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="T30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="U30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="V30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="W30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="X30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="Y30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="Z30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AA30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AB30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AC30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AD30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AE30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AF30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AG30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AH30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AI30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AJ30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AK30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AL30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AM30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AN30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AO30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AP30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AQ30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AR30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AS30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AT30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AU30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AV30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AW30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AX30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AY30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AZ30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BA30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BB30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BC30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BD30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BE30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BF30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BG30">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="31" spans="1:59">
@@ -12710,166 +12710,166 @@
         <v>236</v>
       </c>
       <c r="F31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="G31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="H31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="I31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="J31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="K31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="L31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="M31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="N31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="O31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="P31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="Q31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="R31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="S31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="T31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="U31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="V31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="W31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="X31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="Y31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="Z31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AA31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AB31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AC31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AD31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AE31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AF31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AG31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AH31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AI31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AJ31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AK31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AL31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AM31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AN31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AO31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AP31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AQ31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AR31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AS31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AT31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AU31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AV31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AW31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AX31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AY31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="AZ31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BA31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BB31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BC31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BD31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BE31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BF31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="BG31">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="32" spans="1:59">

--- a/data/initial_state_2026.xlsx
+++ b/data/initial_state_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="14540" activeTab="1"/>
+    <workbookView windowWidth="30240" windowHeight="14540"/>
   </bookViews>
   <sheets>
     <sheet name="global.pars" sheetId="1" r:id="rId1"/>
@@ -3346,7 +3346,7 @@
         <v>24</v>
       </c>
       <c r="C12">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13" spans="1:3">
